--- a/BT/experimentData/raw/NA49 158AGeV.xlsx
+++ b/BT/experimentData/raw/NA49 158AGeV.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-20.04\home\xiaozhou\WorkSpace\NuclearModel\tglaubermc\runglauber_v3.3\BT\expData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-20.04\home\xiaozhou\WorkSpace\NuclearModel\tglaubermc\runglauber_v3.3\BT\experimentData\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B823EB4-F99E-490B-84B9-F817D0F80B2F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD84A72-C084-4D18-B248-0165431E3B51}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="30720" windowHeight="13332" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="30720" windowHeight="13332" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="2011 158A" sheetId="1" r:id="rId1"/>
+    <sheet name="1999 158A" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="12">
   <si>
     <t>y区间</t>
   </si>
@@ -45,14 +46,6 @@
     <t>dn/dy</t>
   </si>
   <si>
-    <t>ylow</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>yup</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>dN/dy</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -63,6 +56,17 @@
   <si>
     <t>https://link.aps.org/doi/10.1103/PhysRevC.83.014901</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dylow</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dyup</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t># Format: x y -dx +dx -dy +dy</t>
   </si>
 </sst>
 </file>
@@ -405,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA18"/>
+  <dimension ref="A1:AA27"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="13" max="19" width="0" hidden="1" customWidth="1"/>
@@ -413,19 +417,19 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="X1" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y1" t="s">
         <v>10</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>6</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>7</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="15" x14ac:dyDescent="0.35">
@@ -501,11 +505,11 @@
         <v>-3.23</v>
       </c>
       <c r="Z2">
-        <f>I2-T2</f>
+        <f t="shared" ref="Z2:Z12" si="0">I2-T2</f>
         <v>24.02</v>
       </c>
       <c r="AA2">
-        <f>2*Z2/352</f>
+        <f t="shared" ref="AA2:AA12" si="1">2*Z2/352</f>
         <v>0.13647727272727272</v>
       </c>
     </row>
@@ -553,19 +557,19 @@
         <v>0.13</v>
       </c>
       <c r="X3">
-        <f t="shared" ref="X3:X12" si="0">B3-2.91</f>
+        <f t="shared" ref="X3:X12" si="2">B3-2.91</f>
         <v>-3.23</v>
       </c>
       <c r="Y3">
-        <f t="shared" ref="Y3:Y12" si="1">F3-2.91</f>
+        <f t="shared" ref="Y3:Y12" si="3">F3-2.91</f>
         <v>-3.0300000000000002</v>
       </c>
       <c r="Z3">
-        <f>I3-T3</f>
+        <f t="shared" si="0"/>
         <v>25.88</v>
       </c>
       <c r="AA3">
-        <f>2*Z3/352</f>
+        <f t="shared" si="1"/>
         <v>0.14704545454545453</v>
       </c>
     </row>
@@ -634,19 +638,19 @@
         <v>0.12</v>
       </c>
       <c r="X4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-3.0300000000000002</v>
       </c>
       <c r="Y4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-2.83</v>
       </c>
       <c r="Z4">
-        <f>I4-T4</f>
+        <f t="shared" si="0"/>
         <v>25.76</v>
       </c>
       <c r="AA4">
-        <f>2*Z4/352</f>
+        <f t="shared" si="1"/>
         <v>0.14636363636363636</v>
       </c>
     </row>
@@ -694,19 +698,19 @@
         <v>0.12</v>
       </c>
       <c r="X5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-2.83</v>
       </c>
       <c r="Y5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-2.63</v>
       </c>
       <c r="Z5">
-        <f>I5-T5</f>
+        <f t="shared" si="0"/>
         <v>26.32</v>
       </c>
       <c r="AA5">
-        <f>2*Z5/352</f>
+        <f t="shared" si="1"/>
         <v>0.14954545454545454</v>
       </c>
     </row>
@@ -775,19 +779,19 @@
         <v>0.11</v>
       </c>
       <c r="X6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-2.63</v>
       </c>
       <c r="Y6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-2.4300000000000002</v>
       </c>
       <c r="Z6">
-        <f>I6-T6</f>
+        <f t="shared" si="0"/>
         <v>26.169999999999998</v>
       </c>
       <c r="AA6">
-        <f>2*Z6/352</f>
+        <f t="shared" si="1"/>
         <v>0.14869318181818181</v>
       </c>
     </row>
@@ -835,19 +839,19 @@
         <v>0.11</v>
       </c>
       <c r="X7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-2.4300000000000002</v>
       </c>
       <c r="Y7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-2.23</v>
       </c>
       <c r="Z7">
-        <f>I7-T7</f>
+        <f t="shared" si="0"/>
         <v>27.439999999999998</v>
       </c>
       <c r="AA7">
-        <f>2*Z7/352</f>
+        <f t="shared" si="1"/>
         <v>0.15590909090909089</v>
       </c>
     </row>
@@ -916,19 +920,19 @@
         <v>0.1</v>
       </c>
       <c r="X8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-2.23</v>
       </c>
       <c r="Y8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-2.0300000000000002</v>
       </c>
       <c r="Z8">
-        <f>I8-T8</f>
+        <f t="shared" si="0"/>
         <v>29.990000000000002</v>
       </c>
       <c r="AA8">
-        <f>2*Z8/352</f>
+        <f t="shared" si="1"/>
         <v>0.17039772727272728</v>
       </c>
     </row>
@@ -976,19 +980,19 @@
         <v>0.1</v>
       </c>
       <c r="X9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-2.0300000000000002</v>
       </c>
       <c r="Y9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-1.83</v>
       </c>
       <c r="Z9">
-        <f>I9-T9</f>
+        <f t="shared" si="0"/>
         <v>29.200000000000003</v>
       </c>
       <c r="AA9">
-        <f>2*Z9/352</f>
+        <f t="shared" si="1"/>
         <v>0.16590909090909092</v>
       </c>
     </row>
@@ -1057,19 +1061,19 @@
         <v>0.1</v>
       </c>
       <c r="X10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-1.83</v>
       </c>
       <c r="Y10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-1.6300000000000001</v>
       </c>
       <c r="Z10">
-        <f>I10-T10</f>
+        <f t="shared" si="0"/>
         <v>31.75</v>
       </c>
       <c r="AA10">
-        <f>2*Z10/352</f>
+        <f t="shared" si="1"/>
         <v>0.18039772727272727</v>
       </c>
     </row>
@@ -1117,19 +1121,19 @@
         <v>0.1</v>
       </c>
       <c r="X11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-1.6300000000000001</v>
       </c>
       <c r="Y11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-1.4300000000000002</v>
       </c>
       <c r="Z11">
-        <f>I11-T11</f>
+        <f t="shared" si="0"/>
         <v>38.24</v>
       </c>
       <c r="AA11">
-        <f>2*Z11/352</f>
+        <f t="shared" si="1"/>
         <v>0.21727272727272728</v>
       </c>
     </row>
@@ -1174,19 +1178,19 @@
         <v>0</v>
       </c>
       <c r="X12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-1.4300000000000002</v>
       </c>
       <c r="Y12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-1.2300000000000002</v>
       </c>
       <c r="Z12">
-        <f>I12-T12</f>
+        <f t="shared" si="0"/>
         <v>39.35</v>
       </c>
       <c r="AA12">
-        <f>2*Z12/352</f>
+        <f t="shared" si="1"/>
         <v>0.22357954545454548</v>
       </c>
     </row>
@@ -1199,11 +1203,260 @@
     <row r="16" spans="1:27" ht="15" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
     </row>
-    <row r="17" spans="1:1" ht="15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="15" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
-    </row>
-    <row r="18" spans="1:1" ht="15" x14ac:dyDescent="0.35">
+      <c r="D17">
+        <f>(E17+F17)/2</f>
+        <v>-0.42000000000000004</v>
+      </c>
+      <c r="E17">
+        <v>-0.52</v>
+      </c>
+      <c r="F17">
+        <v>-0.32</v>
+      </c>
+      <c r="G17">
+        <v>24.02</v>
+      </c>
+      <c r="H17">
+        <f t="shared" ref="H17:H27" si="4">SQRT(K2*K2+V2*V2)</f>
+        <v>1.4159802258506295</v>
+      </c>
+      <c r="I17">
+        <f>G17*0.07</f>
+        <v>1.6814000000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
+      <c r="D18">
+        <f t="shared" ref="D18:D27" si="5">(E18+F18)/2</f>
+        <v>-0.22</v>
+      </c>
+      <c r="E18">
+        <v>-0.32</v>
+      </c>
+      <c r="F18">
+        <v>-0.12</v>
+      </c>
+      <c r="G18">
+        <v>25.88</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="4"/>
+        <v>1.2467958934805647</v>
+      </c>
+      <c r="I18">
+        <f t="shared" ref="I18:I27" si="6">G18*0.07</f>
+        <v>1.8116000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D19">
+        <f t="shared" si="5"/>
+        <v>-1.9999999999999997E-2</v>
+      </c>
+      <c r="E19">
+        <v>-0.12</v>
+      </c>
+      <c r="F19">
+        <v>0.08</v>
+      </c>
+      <c r="G19">
+        <v>25.76</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="4"/>
+        <v>1.0965856099730655</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="6"/>
+        <v>1.8032000000000004</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D20">
+        <f t="shared" si="5"/>
+        <v>0.18000000000000002</v>
+      </c>
+      <c r="E20">
+        <v>0.08</v>
+      </c>
+      <c r="F20">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G20">
+        <v>26.32</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="4"/>
+        <v>1.0171037311896953</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="6"/>
+        <v>1.8424000000000003</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D21">
+        <f t="shared" si="5"/>
+        <v>0.38</v>
+      </c>
+      <c r="E21">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="F21">
+        <v>0.48</v>
+      </c>
+      <c r="G21">
+        <v>26.169999999999998</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="4"/>
+        <v>0.94641428560646734</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="6"/>
+        <v>1.8319000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D22">
+        <f t="shared" si="5"/>
+        <v>0.58000000000000007</v>
+      </c>
+      <c r="E22">
+        <v>0.48</v>
+      </c>
+      <c r="F22">
+        <v>0.68</v>
+      </c>
+      <c r="G22">
+        <v>27.439999999999998</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="4"/>
+        <v>0.89677198885781439</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="6"/>
+        <v>1.9208000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D23">
+        <f t="shared" si="5"/>
+        <v>0.78</v>
+      </c>
+      <c r="E23">
+        <v>0.68</v>
+      </c>
+      <c r="F23">
+        <v>0.88</v>
+      </c>
+      <c r="G23">
+        <v>29.990000000000002</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="4"/>
+        <v>0.88566359301938113</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="6"/>
+        <v>2.0993000000000004</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D24">
+        <f t="shared" si="5"/>
+        <v>0.98</v>
+      </c>
+      <c r="E24">
+        <v>0.88</v>
+      </c>
+      <c r="F24">
+        <v>1.08</v>
+      </c>
+      <c r="G24">
+        <v>29.200000000000003</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="4"/>
+        <v>0.85586213843118442</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="6"/>
+        <v>2.0440000000000005</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D25">
+        <f t="shared" si="5"/>
+        <v>1.1800000000000002</v>
+      </c>
+      <c r="E25">
+        <v>1.08</v>
+      </c>
+      <c r="F25">
+        <v>1.28</v>
+      </c>
+      <c r="G25">
+        <v>31.75</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="4"/>
+        <v>1.0547511554864493</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="6"/>
+        <v>2.2225000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D26">
+        <f t="shared" si="5"/>
+        <v>1.38</v>
+      </c>
+      <c r="E26">
+        <v>1.28</v>
+      </c>
+      <c r="F26">
+        <v>1.48</v>
+      </c>
+      <c r="G26">
+        <v>38.24</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="4"/>
+        <v>3.4314574163174458</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="6"/>
+        <v>2.6768000000000005</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D27">
+        <f t="shared" si="5"/>
+        <v>1.58</v>
+      </c>
+      <c r="E27">
+        <v>1.48</v>
+      </c>
+      <c r="F27">
+        <v>1.68</v>
+      </c>
+      <c r="G27">
+        <v>39.35</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="6"/>
+        <v>2.7545000000000002</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1212,4 +1465,677 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{442522CB-9026-483E-9FA1-CFE3429FB421}">
+  <dimension ref="A1:N26"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>-3.52</v>
+      </c>
+      <c r="B1">
+        <v>-3.62</v>
+      </c>
+      <c r="C1">
+        <v>-3.42</v>
+      </c>
+      <c r="D1">
+        <v>0.12109499999999999</v>
+      </c>
+      <c r="E1">
+        <v>5.8891199999999998E-2</v>
+      </c>
+      <c r="F1">
+        <v>0</v>
+      </c>
+      <c r="I1">
+        <f t="shared" ref="I1:I16" si="0">A1+2.91</f>
+        <v>-0.60999999999999988</v>
+      </c>
+      <c r="J1">
+        <f t="shared" ref="J1:J16" si="1">B1+2.91</f>
+        <v>-0.71</v>
+      </c>
+      <c r="K1">
+        <f t="shared" ref="K1:K16" si="2">C1+2.91</f>
+        <v>-0.50999999999999979</v>
+      </c>
+      <c r="L1">
+        <v>31.160599999999999</v>
+      </c>
+      <c r="M1">
+        <v>5.2676699999999999</v>
+      </c>
+      <c r="N1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>-3.32</v>
+      </c>
+      <c r="B2">
+        <v>-3.42</v>
+      </c>
+      <c r="C2">
+        <v>-3.22</v>
+      </c>
+      <c r="D2">
+        <v>0.131217</v>
+      </c>
+      <c r="E2">
+        <v>4.7849099999999999E-2</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <f t="shared" si="0"/>
+        <v>-0.4099999999999997</v>
+      </c>
+      <c r="J2">
+        <f t="shared" si="1"/>
+        <v>-0.50999999999999979</v>
+      </c>
+      <c r="K2">
+        <f t="shared" si="2"/>
+        <v>-0.31000000000000005</v>
+      </c>
+      <c r="L2">
+        <v>28.376899999999999</v>
+      </c>
+      <c r="M2">
+        <v>4.3683100000000001</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>-3.12</v>
+      </c>
+      <c r="B3">
+        <v>-3.22</v>
+      </c>
+      <c r="C3">
+        <v>-3.02</v>
+      </c>
+      <c r="D3">
+        <v>0.160663</v>
+      </c>
+      <c r="E3">
+        <v>4.4168399999999997E-2</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <f t="shared" si="0"/>
+        <v>-0.20999999999999996</v>
+      </c>
+      <c r="J3">
+        <f t="shared" si="1"/>
+        <v>-0.31000000000000005</v>
+      </c>
+      <c r="K3">
+        <f t="shared" si="2"/>
+        <v>-0.10999999999999988</v>
+      </c>
+      <c r="L3">
+        <v>27.7516</v>
+      </c>
+      <c r="M3">
+        <v>3.9400400000000002</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>-2.92</v>
+      </c>
+      <c r="B4">
+        <v>-3.02</v>
+      </c>
+      <c r="C4">
+        <v>-2.82</v>
+      </c>
+      <c r="D4">
+        <v>0.177594</v>
+      </c>
+      <c r="E4">
+        <v>4.0487700000000001E-2</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="0"/>
+        <v>-9.9999999999997868E-3</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="1"/>
+        <v>-0.10999999999999988</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="2"/>
+        <v>9.0000000000000302E-2</v>
+      </c>
+      <c r="L4">
+        <v>26.6296</v>
+      </c>
+      <c r="M4">
+        <v>3.5974300000000001</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>-2.72</v>
+      </c>
+      <c r="B5">
+        <v>-2.82</v>
+      </c>
+      <c r="C5">
+        <v>-2.62</v>
+      </c>
+      <c r="D5">
+        <v>0.22728300000000001</v>
+      </c>
+      <c r="E5">
+        <v>3.5886800000000003E-2</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="0"/>
+        <v>0.18999999999999995</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="1"/>
+        <v>9.0000000000000302E-2</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="2"/>
+        <v>0.29000000000000004</v>
+      </c>
+      <c r="L5">
+        <v>28.7623</v>
+      </c>
+      <c r="M5">
+        <v>3.2119900000000001</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>-2.52</v>
+      </c>
+      <c r="B6">
+        <v>-2.62</v>
+      </c>
+      <c r="C6">
+        <v>-2.42</v>
+      </c>
+      <c r="D6">
+        <v>0.27126800000000001</v>
+      </c>
+      <c r="E6">
+        <v>3.1285899999999998E-2</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>0.39000000000000012</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="1"/>
+        <v>0.29000000000000004</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="2"/>
+        <v>0.49000000000000021</v>
+      </c>
+      <c r="L6">
+        <v>30.886500000000002</v>
+      </c>
+      <c r="M6">
+        <v>2.7837299999999998</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>-2.3199999999999998</v>
+      </c>
+      <c r="B7">
+        <v>-2.42</v>
+      </c>
+      <c r="C7">
+        <v>-2.2200000000000002</v>
+      </c>
+      <c r="D7">
+        <v>0.30255300000000002</v>
+      </c>
+      <c r="E7">
+        <v>2.3924500000000001E-2</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>0.5900000000000003</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="1"/>
+        <v>0.49000000000000021</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="2"/>
+        <v>0.69</v>
+      </c>
+      <c r="L7">
+        <v>32</v>
+      </c>
+      <c r="M7">
+        <v>2.14133</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>-2.12</v>
+      </c>
+      <c r="B8">
+        <v>-2.2200000000000002</v>
+      </c>
+      <c r="C8">
+        <v>-2.02</v>
+      </c>
+      <c r="D8">
+        <v>0.34662999999999999</v>
+      </c>
+      <c r="E8">
+        <v>2.1163999999999999E-2</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>0.79</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="1"/>
+        <v>0.69</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="2"/>
+        <v>0.89000000000000012</v>
+      </c>
+      <c r="L8">
+        <v>34.646700000000003</v>
+      </c>
+      <c r="M8">
+        <v>1.8843700000000001</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>-1.92</v>
+      </c>
+      <c r="B9">
+        <v>-2.02</v>
+      </c>
+      <c r="C9">
+        <v>-1.82</v>
+      </c>
+      <c r="D9">
+        <v>0.36033999999999999</v>
+      </c>
+      <c r="E9">
+        <v>1.74833E-2</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>0.99000000000000021</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="1"/>
+        <v>0.89000000000000012</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="2"/>
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="L9">
+        <v>34.9893</v>
+      </c>
+      <c r="M9">
+        <v>1.54176</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>-1.72</v>
+      </c>
+      <c r="B10">
+        <v>-1.82</v>
+      </c>
+      <c r="C10">
+        <v>-1.62</v>
+      </c>
+      <c r="D10">
+        <v>0.37892799999999999</v>
+      </c>
+      <c r="E10">
+        <v>1.84035E-2</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="0"/>
+        <v>1.1900000000000002</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="1"/>
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="2"/>
+        <v>1.29</v>
+      </c>
+      <c r="L10">
+        <v>36</v>
+      </c>
+      <c r="M10">
+        <v>1.54176</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>-1.52</v>
+      </c>
+      <c r="B11">
+        <v>-1.62</v>
+      </c>
+      <c r="C11">
+        <v>-1.42</v>
+      </c>
+      <c r="D11">
+        <v>0.37616699999999997</v>
+      </c>
+      <c r="E11">
+        <v>2.2084199999999998E-2</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="0"/>
+        <v>1.3900000000000001</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="1"/>
+        <v>1.29</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="2"/>
+        <v>1.4900000000000002</v>
+      </c>
+      <c r="L11">
+        <v>35.5032</v>
+      </c>
+      <c r="M11">
+        <v>1.84154</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>-1.32</v>
+      </c>
+      <c r="B12">
+        <v>-1.42</v>
+      </c>
+      <c r="C12">
+        <v>-1.22</v>
+      </c>
+      <c r="D12">
+        <v>0.350495</v>
+      </c>
+      <c r="E12">
+        <v>1.74833E-2</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>1.59</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="1"/>
+        <v>1.4900000000000002</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="2"/>
+        <v>1.6900000000000002</v>
+      </c>
+      <c r="L12">
+        <v>33.113500000000002</v>
+      </c>
+      <c r="M12">
+        <v>1.54176</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>-1.1200000000000001</v>
+      </c>
+      <c r="B13">
+        <v>-1.22</v>
+      </c>
+      <c r="C13">
+        <v>-1.02</v>
+      </c>
+      <c r="D13">
+        <v>0.30071300000000001</v>
+      </c>
+      <c r="E13">
+        <v>1.38026E-2</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="0"/>
+        <v>1.79</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="1"/>
+        <v>1.6900000000000002</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="2"/>
+        <v>1.8900000000000001</v>
+      </c>
+      <c r="L13">
+        <v>28.8565</v>
+      </c>
+      <c r="M13">
+        <v>1.1991400000000001</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>-0.92</v>
+      </c>
+      <c r="B14">
+        <v>-1.02</v>
+      </c>
+      <c r="C14">
+        <v>-0.82</v>
+      </c>
+      <c r="D14">
+        <v>0.25323200000000001</v>
+      </c>
+      <c r="E14">
+        <v>1.6563100000000001E-2</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="0"/>
+        <v>1.9900000000000002</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="1"/>
+        <v>1.8900000000000001</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="2"/>
+        <v>2.0900000000000003</v>
+      </c>
+      <c r="L14">
+        <v>24.907900000000001</v>
+      </c>
+      <c r="M14">
+        <v>1.4560999999999999</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>-0.72</v>
+      </c>
+      <c r="B15">
+        <v>-0.82</v>
+      </c>
+      <c r="C15">
+        <v>-0.62</v>
+      </c>
+      <c r="D15">
+        <v>0.18900400000000001</v>
+      </c>
+      <c r="E15">
+        <v>1.38026E-2</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="0"/>
+        <v>2.1900000000000004</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="1"/>
+        <v>2.0900000000000003</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="2"/>
+        <v>2.29</v>
+      </c>
+      <c r="L15">
+        <v>19.357600000000001</v>
+      </c>
+      <c r="M15">
+        <v>1.1520300000000001</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>-0.52</v>
+      </c>
+      <c r="B16">
+        <v>-0.62</v>
+      </c>
+      <c r="C16">
+        <v>-0.42</v>
+      </c>
+      <c r="D16">
+        <v>0.17244100000000001</v>
+      </c>
+      <c r="E16">
+        <v>2.9445599999999999E-2</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="0"/>
+        <v>2.39</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="1"/>
+        <v>2.29</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="2"/>
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="L16">
+        <v>18.1328</v>
+      </c>
+      <c r="M16">
+        <v>2.6552500000000001</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/BT/experimentData/raw/NA49 158AGeV.xlsx
+++ b/BT/experimentData/raw/NA49 158AGeV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-20.04\home\xiaozhou\WorkSpace\NuclearModel\tglaubermc\runglauber_v3.3\BT\experimentData\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD84A72-C084-4D18-B248-0165431E3B51}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB194EE9-196B-42E6-9523-B9DFE7F188D6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="30720" windowHeight="13332" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="14">
   <si>
     <t>y区间</t>
   </si>
@@ -66,7 +66,16 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t># Format: x y -dx +dx -dy +dy</t>
+    <t xml:space="preserve">rapidity </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>net baryon dn/dy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">net proton dn/dy </t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -124,10 +133,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1469,10 +1484,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{442522CB-9026-483E-9FA1-CFE3429FB421}">
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="15" x14ac:dyDescent="0.35">
       <c r="A1">
         <v>-3.52</v>
       </c>
@@ -1512,8 +1527,22 @@
       <c r="N1">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="R1" s="4"/>
+      <c r="S1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+    </row>
+    <row r="2" spans="1:24" ht="15" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>-3.32</v>
       </c>
@@ -1553,8 +1582,32 @@
       <c r="N2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q2" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="R2">
+        <v>2.4</v>
+      </c>
+      <c r="S2">
+        <v>31.1</v>
+      </c>
+      <c r="T2" t="s">
+        <v>4</v>
+      </c>
+      <c r="U2">
+        <v>5.3</v>
+      </c>
+      <c r="V2">
+        <v>76.900000000000006</v>
+      </c>
+      <c r="W2" t="s">
+        <v>4</v>
+      </c>
+      <c r="X2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" ht="15" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>-3.12</v>
       </c>
@@ -1594,8 +1647,32 @@
       <c r="N3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q3" s="1">
+        <v>2.4</v>
+      </c>
+      <c r="R3">
+        <v>2.6</v>
+      </c>
+      <c r="S3">
+        <v>28.3</v>
+      </c>
+      <c r="T3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U3">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="V3">
+        <v>71</v>
+      </c>
+      <c r="W3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" ht="15" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>-2.92</v>
       </c>
@@ -1635,8 +1712,32 @@
       <c r="N4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q4" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="R4">
+        <v>2.8</v>
+      </c>
+      <c r="S4">
+        <v>27.8</v>
+      </c>
+      <c r="T4" t="s">
+        <v>4</v>
+      </c>
+      <c r="U4">
+        <v>4</v>
+      </c>
+      <c r="V4">
+        <v>69.900000000000006</v>
+      </c>
+      <c r="W4" t="s">
+        <v>4</v>
+      </c>
+      <c r="X4">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="15" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>-2.72</v>
       </c>
@@ -1676,8 +1777,32 @@
       <c r="N5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q5" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="R5">
+        <v>3</v>
+      </c>
+      <c r="S5">
+        <v>26.6</v>
+      </c>
+      <c r="T5" t="s">
+        <v>4</v>
+      </c>
+      <c r="U5">
+        <v>3.7</v>
+      </c>
+      <c r="V5">
+        <v>67.599999999999994</v>
+      </c>
+      <c r="W5" t="s">
+        <v>4</v>
+      </c>
+      <c r="X5">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="15" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>-2.52</v>
       </c>
@@ -1717,8 +1842,32 @@
       <c r="N6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q6" s="1">
+        <v>3</v>
+      </c>
+      <c r="R6">
+        <v>3.2</v>
+      </c>
+      <c r="S6">
+        <v>28.8</v>
+      </c>
+      <c r="T6" t="s">
+        <v>4</v>
+      </c>
+      <c r="U6">
+        <v>3.3</v>
+      </c>
+      <c r="V6">
+        <v>72.099999999999994</v>
+      </c>
+      <c r="W6" t="s">
+        <v>4</v>
+      </c>
+      <c r="X6">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="15" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>-2.3199999999999998</v>
       </c>
@@ -1758,8 +1907,32 @@
       <c r="N7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q7" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="R7">
+        <v>3.4</v>
+      </c>
+      <c r="S7">
+        <v>30.8</v>
+      </c>
+      <c r="T7" t="s">
+        <v>4</v>
+      </c>
+      <c r="U7">
+        <v>2.8</v>
+      </c>
+      <c r="V7">
+        <v>76.3</v>
+      </c>
+      <c r="W7" t="s">
+        <v>4</v>
+      </c>
+      <c r="X7">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="15" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>-2.12</v>
       </c>
@@ -1799,8 +1972,32 @@
       <c r="N8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q8" s="1">
+        <v>3.4</v>
+      </c>
+      <c r="R8">
+        <v>3.6</v>
+      </c>
+      <c r="S8">
+        <v>32</v>
+      </c>
+      <c r="T8" t="s">
+        <v>4</v>
+      </c>
+      <c r="U8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="V8">
+        <v>78.8</v>
+      </c>
+      <c r="W8" t="s">
+        <v>4</v>
+      </c>
+      <c r="X8">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" ht="15" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>-1.92</v>
       </c>
@@ -1840,8 +2037,32 @@
       <c r="N9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q9" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="R9">
+        <v>3.8</v>
+      </c>
+      <c r="S9">
+        <v>34.6</v>
+      </c>
+      <c r="T9" t="s">
+        <v>4</v>
+      </c>
+      <c r="U9">
+        <v>1.9</v>
+      </c>
+      <c r="V9">
+        <v>84.1</v>
+      </c>
+      <c r="W9" t="s">
+        <v>4</v>
+      </c>
+      <c r="X9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" ht="15" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>-1.72</v>
       </c>
@@ -1881,8 +2102,32 @@
       <c r="N10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q10" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="R10">
+        <v>4</v>
+      </c>
+      <c r="S10">
+        <v>34.9</v>
+      </c>
+      <c r="T10" t="s">
+        <v>4</v>
+      </c>
+      <c r="U10">
+        <v>1.6</v>
+      </c>
+      <c r="V10">
+        <v>84.2</v>
+      </c>
+      <c r="W10" t="s">
+        <v>4</v>
+      </c>
+      <c r="X10">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" ht="15" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>-1.52</v>
       </c>
@@ -1922,8 +2167,32 @@
       <c r="N11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q11" s="1">
+        <v>4</v>
+      </c>
+      <c r="R11">
+        <v>4.2</v>
+      </c>
+      <c r="S11">
+        <v>35.9</v>
+      </c>
+      <c r="T11" t="s">
+        <v>4</v>
+      </c>
+      <c r="U11">
+        <v>1.6</v>
+      </c>
+      <c r="V11">
+        <v>85.6</v>
+      </c>
+      <c r="W11" t="s">
+        <v>4</v>
+      </c>
+      <c r="X11">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" ht="15" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>-1.32</v>
       </c>
@@ -1963,8 +2232,32 @@
       <c r="N12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q12" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="R12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="S12">
+        <v>35.5</v>
+      </c>
+      <c r="T12" t="s">
+        <v>4</v>
+      </c>
+      <c r="U12">
+        <v>1.9</v>
+      </c>
+      <c r="V12">
+        <v>83.3</v>
+      </c>
+      <c r="W12" t="s">
+        <v>4</v>
+      </c>
+      <c r="X12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" ht="15" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>-1.1200000000000001</v>
       </c>
@@ -2004,8 +2297,32 @@
       <c r="N13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q13" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="R13">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="S13">
+        <v>33.1</v>
+      </c>
+      <c r="T13" t="s">
+        <v>4</v>
+      </c>
+      <c r="U13">
+        <v>1.6</v>
+      </c>
+      <c r="V13">
+        <v>76.900000000000006</v>
+      </c>
+      <c r="W13" t="s">
+        <v>4</v>
+      </c>
+      <c r="X13">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" ht="15" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>-0.92</v>
       </c>
@@ -2045,8 +2362,32 @@
       <c r="N14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q14" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="R14">
+        <v>4.8</v>
+      </c>
+      <c r="S14">
+        <v>28.8</v>
+      </c>
+      <c r="T14" t="s">
+        <v>4</v>
+      </c>
+      <c r="U14">
+        <v>1.3</v>
+      </c>
+      <c r="V14">
+        <v>66.2</v>
+      </c>
+      <c r="W14" t="s">
+        <v>4</v>
+      </c>
+      <c r="X14">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" ht="15" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>-0.72</v>
       </c>
@@ -2086,8 +2427,32 @@
       <c r="N15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Q15" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="R15">
+        <v>5</v>
+      </c>
+      <c r="S15">
+        <v>24.8</v>
+      </c>
+      <c r="T15" t="s">
+        <v>4</v>
+      </c>
+      <c r="U15">
+        <v>1.5</v>
+      </c>
+      <c r="V15">
+        <v>56.1</v>
+      </c>
+      <c r="W15" t="s">
+        <v>4</v>
+      </c>
+      <c r="X15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" ht="15" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>-0.52</v>
       </c>
@@ -2127,13 +2492,63 @@
       <c r="N16">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>11</v>
+      <c r="Q16" s="1">
+        <v>5</v>
+      </c>
+      <c r="R16">
+        <v>5.2</v>
+      </c>
+      <c r="S16">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="T16" t="s">
+        <v>4</v>
+      </c>
+      <c r="U16">
+        <v>1.2</v>
+      </c>
+      <c r="V16">
+        <v>43.1</v>
+      </c>
+      <c r="W16" t="s">
+        <v>4</v>
+      </c>
+      <c r="X16">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="17" spans="17:24" ht="15" x14ac:dyDescent="0.35">
+      <c r="Q17" s="1">
+        <v>5.2</v>
+      </c>
+      <c r="R17">
+        <v>5.4</v>
+      </c>
+      <c r="S17">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="T17" t="s">
+        <v>4</v>
+      </c>
+      <c r="U17">
+        <v>2.7</v>
+      </c>
+      <c r="V17">
+        <v>39</v>
+      </c>
+      <c r="W17" t="s">
+        <v>4</v>
+      </c>
+      <c r="X17">
+        <v>5.6</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="S1:U1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="V1:X1"/>
+  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/BT/experimentData/raw/NA49 158AGeV.xlsx
+++ b/BT/experimentData/raw/NA49 158AGeV.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-20.04\home\xiaozhou\WorkSpace\NuclearModel\tglaubermc\runglauber_v3.3\BT\experimentData\raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-20.04\home\xiaozhou\WorkSpace\NuclearModel\tglaubermc\runglauber_v3.3\BT\experimentData\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB194EE9-196B-42E6-9523-B9DFE7F188D6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0BCA58D-F755-4B06-B9E5-E5796DD4F5B4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="30720" windowHeight="13332" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="30720" windowHeight="13332" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2011 158A" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="40">
   <si>
     <t>y区间</t>
   </si>
@@ -77,12 +77,121 @@
     <t xml:space="preserve">net proton dn/dy </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>proton</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>y</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="13.3"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="KaTeX_Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>y</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 区间</t>
+    </r>
+  </si>
+  <si>
+    <t>C0</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>-0.52 ≤ y ≤ -0.32</t>
+  </si>
+  <si>
+    <t>-0.32 ≤ y ≤ -0.12</t>
+  </si>
+  <si>
+    <t>-0.12 ≤ y ≤ 0.08</t>
+  </si>
+  <si>
+    <t>0.08 ≤ y ≤ 0.28</t>
+  </si>
+  <si>
+    <t>0.28 ≤ y ≤ 0.48</t>
+  </si>
+  <si>
+    <t>0.48 ≤ y ≤ 0.68</t>
+  </si>
+  <si>
+    <t>0.68 ≤ y ≤ 0.88</t>
+  </si>
+  <si>
+    <t>0.88 ≤ y ≤ 1.08</t>
+  </si>
+  <si>
+    <t>1.08 ≤ y ≤ 1.28</t>
+  </si>
+  <si>
+    <t>1.28 ≤ y ≤ 1.48</t>
+  </si>
+  <si>
+    <t>1.48 ≤ y ≤ 1.68</t>
+  </si>
+  <si>
+    <t>anti proton</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.52 ≤ y ≤ -0.12</t>
+  </si>
+  <si>
+    <t>-0.12 ≤ y ≤ 0.28</t>
+  </si>
+  <si>
+    <t>0.28 ≤ y ≤ 0.68</t>
+  </si>
+  <si>
+    <t>0.68 ≤ y ≤ 1.08</t>
+  </si>
+  <si>
+    <t>1.08 ≤ y ≤ 1.48</t>
+  </si>
+  <si>
+    <t>Nw</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>,</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="180" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="187" formatCode="0.0000000_);[Red]\(0.0000000\)"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -111,6 +220,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="13.3"/>
+      <color rgb="FF0F1115"/>
+      <name val="KaTeX_Math"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -133,7 +257,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
@@ -143,6 +267,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="187" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -424,13 +550,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA27"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AV66"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="13" max="19" width="0" hidden="1" customWidth="1"/>
+    <col min="31" max="31" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.109375" customWidth="1"/>
+    <col min="34" max="34" width="3.77734375" customWidth="1"/>
+    <col min="35" max="35" width="12.109375" customWidth="1"/>
+    <col min="36" max="36" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="37" max="40" width="12.109375" customWidth="1"/>
+    <col min="41" max="41" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="42" max="44" width="12.109375" customWidth="1"/>
+    <col min="45" max="45" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="49" max="51" width="11" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:48">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -447,7 +587,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:48" ht="15">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -527,8 +667,11 @@
         <f t="shared" ref="AA2:AA12" si="1">2*Z2/352</f>
         <v>0.13647727272727272</v>
       </c>
-    </row>
-    <row r="3" spans="1:27" ht="15" x14ac:dyDescent="0.35">
+      <c r="AE2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:48" ht="17.399999999999999">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -587,8 +730,29 @@
         <f t="shared" si="1"/>
         <v>0.14704545454545453</v>
       </c>
-    </row>
-    <row r="4" spans="1:27" ht="15" x14ac:dyDescent="0.35">
+      <c r="AE3" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:48" ht="17.399999999999999">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -668,8 +832,56 @@
         <f t="shared" si="1"/>
         <v>0.14636363636363636</v>
       </c>
-    </row>
-    <row r="5" spans="1:27" ht="15" x14ac:dyDescent="0.35">
+      <c r="AE4" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF4">
+        <v>25.63</v>
+      </c>
+      <c r="AG4">
+        <v>1.41</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI4">
+        <v>1.61</v>
+      </c>
+      <c r="AJ4">
+        <v>0.13</v>
+      </c>
+      <c r="AL4">
+        <f>(AM4+AN4)/2</f>
+        <v>-0.42000000000000004</v>
+      </c>
+      <c r="AM4">
+        <v>-0.52</v>
+      </c>
+      <c r="AN4">
+        <v>-0.32</v>
+      </c>
+      <c r="AO4">
+        <f>AF4-AI4</f>
+        <v>24.02</v>
+      </c>
+      <c r="AQ4" s="5">
+        <f>SQRT(AG4*AG4+AJ4*AJ4)</f>
+        <v>1.4159802258506295</v>
+      </c>
+      <c r="AR4" s="5"/>
+      <c r="AS4">
+        <f>AO4*0.07</f>
+        <v>1.6814000000000002</v>
+      </c>
+      <c r="AU4">
+        <v>357</v>
+      </c>
+      <c r="AV4" s="6">
+        <f>AO4/AU4</f>
+        <v>6.7282913165266106E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:48" ht="15">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -728,8 +940,56 @@
         <f t="shared" si="1"/>
         <v>0.14954545454545454</v>
       </c>
-    </row>
-    <row r="6" spans="1:27" ht="15" x14ac:dyDescent="0.35">
+      <c r="AE5" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF5">
+        <v>27.49</v>
+      </c>
+      <c r="AG5">
+        <v>1.24</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI5">
+        <v>1.61</v>
+      </c>
+      <c r="AJ5">
+        <v>0.13</v>
+      </c>
+      <c r="AL5">
+        <f t="shared" ref="AL5:AL14" si="4">(AM5+AN5)/2</f>
+        <v>-0.22</v>
+      </c>
+      <c r="AM5">
+        <v>-0.32</v>
+      </c>
+      <c r="AN5">
+        <v>-0.12</v>
+      </c>
+      <c r="AO5">
+        <f>AF5-AI5</f>
+        <v>25.88</v>
+      </c>
+      <c r="AQ5" s="5">
+        <f>SQRT(AG5*AG5+AJ5*AJ5)</f>
+        <v>1.2467958934805647</v>
+      </c>
+      <c r="AR5" s="5"/>
+      <c r="AS5">
+        <f>AO5*0.07</f>
+        <v>1.8116000000000001</v>
+      </c>
+      <c r="AU5">
+        <v>357</v>
+      </c>
+      <c r="AV5" s="6">
+        <f>AO5/AU5</f>
+        <v>7.2492997198879555E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:48" ht="15">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
@@ -809,8 +1069,56 @@
         <f t="shared" si="1"/>
         <v>0.14869318181818181</v>
       </c>
-    </row>
-    <row r="7" spans="1:27" ht="15" x14ac:dyDescent="0.35">
+      <c r="AE6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF6">
+        <v>27.51</v>
+      </c>
+      <c r="AG6">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI6">
+        <v>1.75</v>
+      </c>
+      <c r="AJ6">
+        <v>0.12</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="4"/>
+        <v>-1.9999999999999997E-2</v>
+      </c>
+      <c r="AM6">
+        <v>-0.12</v>
+      </c>
+      <c r="AN6">
+        <v>0.08</v>
+      </c>
+      <c r="AO6">
+        <f>AF6-AI6</f>
+        <v>25.76</v>
+      </c>
+      <c r="AQ6" s="5">
+        <f>SQRT(AG6*AG6+AJ6*AJ6)</f>
+        <v>1.0965856099730655</v>
+      </c>
+      <c r="AR6" s="5"/>
+      <c r="AS6">
+        <f>AO6*0.07</f>
+        <v>1.8032000000000004</v>
+      </c>
+      <c r="AU6">
+        <v>357</v>
+      </c>
+      <c r="AV6" s="6">
+        <f>AO6/AU6</f>
+        <v>7.2156862745098041E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:48" ht="15">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -869,8 +1177,56 @@
         <f t="shared" si="1"/>
         <v>0.15590909090909089</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" ht="15" x14ac:dyDescent="0.35">
+      <c r="AE7" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF7">
+        <v>28.07</v>
+      </c>
+      <c r="AG7">
+        <v>1.01</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI7">
+        <v>1.75</v>
+      </c>
+      <c r="AJ7">
+        <v>0.12</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="4"/>
+        <v>0.18000000000000002</v>
+      </c>
+      <c r="AM7">
+        <v>0.08</v>
+      </c>
+      <c r="AN7">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AO7">
+        <f>AF7-AI7</f>
+        <v>26.32</v>
+      </c>
+      <c r="AQ7" s="5">
+        <f>SQRT(AG7*AG7+AJ7*AJ7)</f>
+        <v>1.0171037311896953</v>
+      </c>
+      <c r="AR7" s="5"/>
+      <c r="AS7">
+        <f>AO7*0.07</f>
+        <v>1.8424000000000003</v>
+      </c>
+      <c r="AU7">
+        <v>357</v>
+      </c>
+      <c r="AV7" s="6">
+        <f>AO7/AU7</f>
+        <v>7.3725490196078436E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:48" ht="15">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
@@ -950,8 +1306,56 @@
         <f t="shared" si="1"/>
         <v>0.17039772727272728</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" ht="15" x14ac:dyDescent="0.35">
+      <c r="AE8" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF8">
+        <v>27.93</v>
+      </c>
+      <c r="AG8">
+        <v>0.94</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI8">
+        <v>1.76</v>
+      </c>
+      <c r="AJ8">
+        <v>0.11</v>
+      </c>
+      <c r="AL8">
+        <f t="shared" si="4"/>
+        <v>0.38</v>
+      </c>
+      <c r="AM8">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AN8">
+        <v>0.48</v>
+      </c>
+      <c r="AO8">
+        <f>AF8-AI8</f>
+        <v>26.169999999999998</v>
+      </c>
+      <c r="AQ8" s="5">
+        <f>SQRT(AG8*AG8+AJ8*AJ8)</f>
+        <v>0.94641428560646734</v>
+      </c>
+      <c r="AR8" s="5"/>
+      <c r="AS8">
+        <f>AO8*0.07</f>
+        <v>1.8319000000000001</v>
+      </c>
+      <c r="AU8">
+        <v>357</v>
+      </c>
+      <c r="AV8" s="6">
+        <f>AO8/AU8</f>
+        <v>7.3305322128851533E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:48" ht="15">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
@@ -1010,8 +1414,56 @@
         <f t="shared" si="1"/>
         <v>0.16590909090909092</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" ht="15" x14ac:dyDescent="0.35">
+      <c r="AE9" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF9">
+        <v>29.2</v>
+      </c>
+      <c r="AG9">
+        <v>0.89</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI9">
+        <v>1.76</v>
+      </c>
+      <c r="AJ9">
+        <v>0.11</v>
+      </c>
+      <c r="AL9">
+        <f t="shared" si="4"/>
+        <v>0.58000000000000007</v>
+      </c>
+      <c r="AM9">
+        <v>0.48</v>
+      </c>
+      <c r="AN9">
+        <v>0.68</v>
+      </c>
+      <c r="AO9">
+        <f>AF9-AI9</f>
+        <v>27.439999999999998</v>
+      </c>
+      <c r="AQ9" s="5">
+        <f>SQRT(AG9*AG9+AJ9*AJ9)</f>
+        <v>0.89677198885781439</v>
+      </c>
+      <c r="AR9" s="5"/>
+      <c r="AS9">
+        <f>AO9*0.07</f>
+        <v>1.9208000000000001</v>
+      </c>
+      <c r="AU9">
+        <v>357</v>
+      </c>
+      <c r="AV9" s="6">
+        <f>AO9/AU9</f>
+        <v>7.6862745098039212E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:48" ht="15">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1091,8 +1543,56 @@
         <f t="shared" si="1"/>
         <v>0.18039772727272727</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" ht="15" x14ac:dyDescent="0.35">
+      <c r="AE10" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF10">
+        <v>31.3</v>
+      </c>
+      <c r="AG10">
+        <v>0.88</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI10">
+        <v>1.31</v>
+      </c>
+      <c r="AJ10">
+        <v>0.1</v>
+      </c>
+      <c r="AL10">
+        <f t="shared" si="4"/>
+        <v>0.78</v>
+      </c>
+      <c r="AM10">
+        <v>0.68</v>
+      </c>
+      <c r="AN10">
+        <v>0.88</v>
+      </c>
+      <c r="AO10">
+        <f>AF10-AI10</f>
+        <v>29.990000000000002</v>
+      </c>
+      <c r="AQ10" s="5">
+        <f>SQRT(AG10*AG10+AJ10*AJ10)</f>
+        <v>0.88566359301938113</v>
+      </c>
+      <c r="AR10" s="5"/>
+      <c r="AS10">
+        <f>AO10*0.07</f>
+        <v>2.0993000000000004</v>
+      </c>
+      <c r="AU10">
+        <v>357</v>
+      </c>
+      <c r="AV10" s="6">
+        <f>AO10/AU10</f>
+        <v>8.4005602240896371E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:48" ht="15">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
@@ -1151,8 +1651,56 @@
         <f t="shared" si="1"/>
         <v>0.21727272727272728</v>
       </c>
-    </row>
-    <row r="12" spans="1:27" ht="15" x14ac:dyDescent="0.35">
+      <c r="AE11" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF11">
+        <v>30.51</v>
+      </c>
+      <c r="AG11">
+        <v>0.85</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI11">
+        <v>1.31</v>
+      </c>
+      <c r="AJ11">
+        <v>0.1</v>
+      </c>
+      <c r="AL11">
+        <f t="shared" si="4"/>
+        <v>0.98</v>
+      </c>
+      <c r="AM11">
+        <v>0.88</v>
+      </c>
+      <c r="AN11">
+        <v>1.08</v>
+      </c>
+      <c r="AO11">
+        <f>AF11-AI11</f>
+        <v>29.200000000000003</v>
+      </c>
+      <c r="AQ11" s="5">
+        <f>SQRT(AG11*AG11+AJ11*AJ11)</f>
+        <v>0.85586213843118442</v>
+      </c>
+      <c r="AR11" s="5"/>
+      <c r="AS11">
+        <f>AO11*0.07</f>
+        <v>2.0440000000000005</v>
+      </c>
+      <c r="AU11">
+        <v>357</v>
+      </c>
+      <c r="AV11" s="6">
+        <f>AO11/AU11</f>
+        <v>8.1792717086834749E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:48" ht="15">
       <c r="A12" s="1" t="s">
         <v>0</v>
       </c>
@@ -1208,17 +1756,198 @@
         <f t="shared" si="1"/>
         <v>0.22357954545454548</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" ht="15" x14ac:dyDescent="0.35">
+      <c r="AE12" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF12">
+        <v>32.35</v>
+      </c>
+      <c r="AG12">
+        <v>1.05</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI12">
+        <v>0.6</v>
+      </c>
+      <c r="AJ12">
+        <v>0.1</v>
+      </c>
+      <c r="AL12">
+        <f t="shared" si="4"/>
+        <v>1.1800000000000002</v>
+      </c>
+      <c r="AM12">
+        <v>1.08</v>
+      </c>
+      <c r="AN12">
+        <v>1.28</v>
+      </c>
+      <c r="AO12">
+        <f>AF12-AI12</f>
+        <v>31.75</v>
+      </c>
+      <c r="AQ12" s="5">
+        <f>SQRT(AG12*AG12+AJ12*AJ12)</f>
+        <v>1.0547511554864493</v>
+      </c>
+      <c r="AR12" s="5"/>
+      <c r="AS12">
+        <f>AO12*0.07</f>
+        <v>2.2225000000000001</v>
+      </c>
+      <c r="AU12">
+        <v>357</v>
+      </c>
+      <c r="AV12" s="6">
+        <f>AO12/AU12</f>
+        <v>8.893557422969188E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:48">
+      <c r="AE13" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF13">
+        <v>38.840000000000003</v>
+      </c>
+      <c r="AG13">
+        <v>3.43</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>37</v>
+      </c>
+      <c r="AI13">
+        <v>0.6</v>
+      </c>
+      <c r="AJ13">
+        <v>0.1</v>
+      </c>
+      <c r="AL13">
+        <f t="shared" si="4"/>
+        <v>1.38</v>
+      </c>
+      <c r="AM13">
+        <v>1.28</v>
+      </c>
+      <c r="AN13">
+        <v>1.48</v>
+      </c>
+      <c r="AO13">
+        <f>AF13-AI13</f>
+        <v>38.24</v>
+      </c>
+      <c r="AQ13" s="5">
+        <f>SQRT(AG13*AG13+AJ13*AJ13)</f>
+        <v>3.4314574163174458</v>
+      </c>
+      <c r="AR13" s="5"/>
+      <c r="AS13">
+        <f>AO13*0.07</f>
+        <v>2.6768000000000005</v>
+      </c>
+      <c r="AU13">
+        <v>357</v>
+      </c>
+      <c r="AV13" s="6">
+        <f>AO13/AU13</f>
+        <v>0.10711484593837535</v>
+      </c>
+    </row>
+    <row r="14" spans="1:48" ht="15">
       <c r="A14" s="1"/>
-    </row>
-    <row r="15" spans="1:27" ht="15" x14ac:dyDescent="0.35">
+      <c r="AE14" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF14">
+        <v>39.35</v>
+      </c>
+      <c r="AG14">
+        <v>2</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>37</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <f t="shared" si="4"/>
+        <v>1.58</v>
+      </c>
+      <c r="AM14">
+        <v>1.48</v>
+      </c>
+      <c r="AN14">
+        <v>1.68</v>
+      </c>
+      <c r="AO14">
+        <f>AF14-AI14</f>
+        <v>39.35</v>
+      </c>
+      <c r="AQ14" s="5">
+        <f>SQRT(AG14*AG14+AJ14*AJ14)</f>
+        <v>2</v>
+      </c>
+      <c r="AR14" s="5"/>
+      <c r="AS14">
+        <f>AO14*0.07</f>
+        <v>2.7545000000000002</v>
+      </c>
+      <c r="AU14">
+        <v>357</v>
+      </c>
+      <c r="AV14" s="6">
+        <f>AO14/AU14</f>
+        <v>0.11022408963585435</v>
+      </c>
+    </row>
+    <row r="15" spans="1:48" ht="15">
       <c r="A15" s="1"/>
-    </row>
-    <row r="16" spans="1:27" ht="15" x14ac:dyDescent="0.35">
+      <c r="AO15">
+        <f>AF15-AI15</f>
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="5">
+        <f>SQRT(AG15*AG15+AJ15*AJ15)</f>
+        <v>0</v>
+      </c>
+      <c r="AR15" s="5"/>
+      <c r="AS15">
+        <f>AO15*0.07</f>
+        <v>0</v>
+      </c>
+      <c r="AV15" s="6" t="e">
+        <f>AO15/AU15</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:48" ht="15">
       <c r="A16" s="1"/>
-    </row>
-    <row r="17" spans="1:9" ht="15" x14ac:dyDescent="0.35">
+      <c r="AF16" t="s">
+        <v>17</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>17</v>
+      </c>
+      <c r="AO16" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ16" s="5">
+        <f>SQRT(AG16*AG16+AJ16*AJ16)</f>
+        <v>0</v>
+      </c>
+      <c r="AR16" s="5"/>
+      <c r="AS16" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV16" s="6" t="e">
+        <f>AO16/AU16</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:48" ht="15">
       <c r="A17" s="1"/>
       <c r="D17">
         <f>(E17+F17)/2</f>
@@ -1234,18 +1963,68 @@
         <v>24.02</v>
       </c>
       <c r="H17">
-        <f t="shared" ref="H17:H27" si="4">SQRT(K2*K2+V2*V2)</f>
+        <f t="shared" ref="H17:H27" si="5">SQRT(K2*K2+V2*V2)</f>
         <v>1.4159802258506295</v>
       </c>
       <c r="I17">
         <f>G17*0.07</f>
         <v>1.6814000000000002</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" ht="15" x14ac:dyDescent="0.35">
+      <c r="AE17" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF17">
+        <v>22.17</v>
+      </c>
+      <c r="AG17">
+        <v>0.74</v>
+      </c>
+      <c r="AI17">
+        <v>1.37</v>
+      </c>
+      <c r="AJ17">
+        <v>0.09</v>
+      </c>
+      <c r="AL17">
+        <f>(AM17+AN17)/2</f>
+        <v>-0.42000000000000004</v>
+      </c>
+      <c r="AM17">
+        <v>-0.52</v>
+      </c>
+      <c r="AN17">
+        <v>-0.32</v>
+      </c>
+      <c r="AO17">
+        <f>AF17-AI17</f>
+        <v>20.8</v>
+      </c>
+      <c r="AP17" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ17" s="5">
+        <f>SQRT(AG17*AG17+AJ17*AJ17)</f>
+        <v>0.74545288248151542</v>
+      </c>
+      <c r="AR17" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS17">
+        <f>AO17*0.07</f>
+        <v>1.4560000000000002</v>
+      </c>
+      <c r="AU17">
+        <v>288</v>
+      </c>
+      <c r="AV17" s="6">
+        <f>AO17/AU17</f>
+        <v>7.2222222222222229E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:48" ht="15">
       <c r="A18" s="1"/>
       <c r="D18">
-        <f t="shared" ref="D18:D27" si="5">(E18+F18)/2</f>
+        <f t="shared" ref="D18:D27" si="6">(E18+F18)/2</f>
         <v>-0.22</v>
       </c>
       <c r="E18">
@@ -1258,17 +2037,67 @@
         <v>25.88</v>
       </c>
       <c r="H18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.2467958934805647</v>
       </c>
       <c r="I18">
-        <f t="shared" ref="I18:I27" si="6">G18*0.07</f>
+        <f t="shared" ref="I18:I27" si="7">G18*0.07</f>
         <v>1.8116000000000001</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="AE18" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF18">
+        <v>22.32</v>
+      </c>
+      <c r="AG18">
+        <v>0.61</v>
+      </c>
+      <c r="AI18">
+        <v>1.37</v>
+      </c>
+      <c r="AJ18">
+        <v>0.09</v>
+      </c>
+      <c r="AL18">
+        <f t="shared" ref="AL18:AL27" si="8">(AM18+AN18)/2</f>
+        <v>-0.22</v>
+      </c>
+      <c r="AM18">
+        <v>-0.32</v>
+      </c>
+      <c r="AN18">
+        <v>-0.12</v>
+      </c>
+      <c r="AO18">
+        <f>AF18-AI18</f>
+        <v>20.95</v>
+      </c>
+      <c r="AP18" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ18" s="5">
+        <f>SQRT(AG18*AG18+AJ18*AJ18)</f>
+        <v>0.61660360037871975</v>
+      </c>
+      <c r="AR18" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS18">
+        <f>AO18*0.07</f>
+        <v>1.4665000000000001</v>
+      </c>
+      <c r="AU18">
+        <v>288</v>
+      </c>
+      <c r="AV18" s="6">
+        <f>AO18/AU18</f>
+        <v>7.2743055555555547E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:48">
       <c r="D19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-1.9999999999999997E-2</v>
       </c>
       <c r="E19">
@@ -1281,17 +2110,67 @@
         <v>25.76</v>
       </c>
       <c r="H19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.0965856099730655</v>
       </c>
       <c r="I19">
+        <f t="shared" si="7"/>
+        <v>1.8032000000000004</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF19">
+        <v>20.97</v>
+      </c>
+      <c r="AG19">
+        <v>0.52</v>
+      </c>
+      <c r="AI19">
+        <v>1.37</v>
+      </c>
+      <c r="AJ19">
+        <v>0.08</v>
+      </c>
+      <c r="AL19">
+        <f t="shared" si="8"/>
+        <v>-1.9999999999999997E-2</v>
+      </c>
+      <c r="AM19">
+        <v>-0.12</v>
+      </c>
+      <c r="AN19">
+        <v>0.08</v>
+      </c>
+      <c r="AO19">
+        <f>AF19-AI19</f>
+        <v>19.599999999999998</v>
+      </c>
+      <c r="AP19" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ19" s="5">
+        <f>SQRT(AG19*AG19+AJ19*AJ19)</f>
+        <v>0.52611785751863627</v>
+      </c>
+      <c r="AR19" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS19">
+        <f>AO19*0.07</f>
+        <v>1.3719999999999999</v>
+      </c>
+      <c r="AU19">
+        <v>288</v>
+      </c>
+      <c r="AV19" s="6">
+        <f>AO19/AU19</f>
+        <v>6.805555555555555E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:48">
+      <c r="D20">
         <f t="shared" si="6"/>
-        <v>1.8032000000000004</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D20">
-        <f t="shared" si="5"/>
         <v>0.18000000000000002</v>
       </c>
       <c r="E20">
@@ -1304,17 +2183,67 @@
         <v>26.32</v>
       </c>
       <c r="H20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.0171037311896953</v>
       </c>
       <c r="I20">
+        <f t="shared" si="7"/>
+        <v>1.8424000000000003</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF20">
+        <v>21.81</v>
+      </c>
+      <c r="AG20">
+        <v>0.51</v>
+      </c>
+      <c r="AI20">
+        <v>1.37</v>
+      </c>
+      <c r="AJ20">
+        <v>0.08</v>
+      </c>
+      <c r="AL20">
+        <f t="shared" si="8"/>
+        <v>0.18000000000000002</v>
+      </c>
+      <c r="AM20">
+        <v>0.08</v>
+      </c>
+      <c r="AN20">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AO20">
+        <f>AF20-AI20</f>
+        <v>20.439999999999998</v>
+      </c>
+      <c r="AP20" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ20" s="5">
+        <f>SQRT(AG20*AG20+AJ20*AJ20)</f>
+        <v>0.51623637996561222</v>
+      </c>
+      <c r="AR20" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS20">
+        <f>AO20*0.07</f>
+        <v>1.4308000000000001</v>
+      </c>
+      <c r="AU20">
+        <v>288</v>
+      </c>
+      <c r="AV20" s="6">
+        <f>AO20/AU20</f>
+        <v>7.0972222222222214E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:48">
+      <c r="D21">
         <f t="shared" si="6"/>
-        <v>1.8424000000000003</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D21">
-        <f t="shared" si="5"/>
         <v>0.38</v>
       </c>
       <c r="E21">
@@ -1327,17 +2256,67 @@
         <v>26.169999999999998</v>
       </c>
       <c r="H21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.94641428560646734</v>
       </c>
       <c r="I21">
+        <f t="shared" si="7"/>
+        <v>1.8319000000000001</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF21">
+        <v>21.74</v>
+      </c>
+      <c r="AG21">
+        <v>0.52</v>
+      </c>
+      <c r="AI21">
+        <v>1.43</v>
+      </c>
+      <c r="AJ21">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AL21">
+        <f t="shared" si="8"/>
+        <v>0.38</v>
+      </c>
+      <c r="AM21">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AN21">
+        <v>0.48</v>
+      </c>
+      <c r="AO21">
+        <f>AF21-AI21</f>
+        <v>20.309999999999999</v>
+      </c>
+      <c r="AP21" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ21" s="5">
+        <f>SQRT(AG21*AG21+AJ21*AJ21)</f>
+        <v>0.52469038489379627</v>
+      </c>
+      <c r="AR21" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS21">
+        <f>AO21*0.07</f>
+        <v>1.4217</v>
+      </c>
+      <c r="AU21">
+        <v>288</v>
+      </c>
+      <c r="AV21" s="6">
+        <f>AO21/AU21</f>
+        <v>7.0520833333333324E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:48">
+      <c r="D22">
         <f t="shared" si="6"/>
-        <v>1.8319000000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D22">
-        <f t="shared" si="5"/>
         <v>0.58000000000000007</v>
       </c>
       <c r="E22">
@@ -1350,17 +2329,67 @@
         <v>27.439999999999998</v>
       </c>
       <c r="H22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.89677198885781439</v>
       </c>
       <c r="I22">
+        <f t="shared" si="7"/>
+        <v>1.9208000000000001</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF22">
+        <v>22.91</v>
+      </c>
+      <c r="AG22">
+        <v>0.5</v>
+      </c>
+      <c r="AI22">
+        <v>1.43</v>
+      </c>
+      <c r="AJ22">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AL22">
+        <f t="shared" si="8"/>
+        <v>0.58000000000000007</v>
+      </c>
+      <c r="AM22">
+        <v>0.48</v>
+      </c>
+      <c r="AN22">
+        <v>0.68</v>
+      </c>
+      <c r="AO22">
+        <f>AF22-AI22</f>
+        <v>21.48</v>
+      </c>
+      <c r="AP22" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ22" s="5">
+        <f>SQRT(AG22*AG22+AJ22*AJ22)</f>
+        <v>0.50487622245457353</v>
+      </c>
+      <c r="AR22" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS22">
+        <f>AO22*0.07</f>
+        <v>1.5036000000000003</v>
+      </c>
+      <c r="AU22">
+        <v>288</v>
+      </c>
+      <c r="AV22" s="6">
+        <f>AO22/AU22</f>
+        <v>7.4583333333333335E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:48">
+      <c r="D23">
         <f t="shared" si="6"/>
-        <v>1.9208000000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D23">
-        <f t="shared" si="5"/>
         <v>0.78</v>
       </c>
       <c r="E23">
@@ -1373,17 +2402,67 @@
         <v>29.990000000000002</v>
       </c>
       <c r="H23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.88566359301938113</v>
       </c>
       <c r="I23">
+        <f t="shared" si="7"/>
+        <v>2.0993000000000004</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF23">
+        <v>23.96</v>
+      </c>
+      <c r="AG23">
+        <v>0.49</v>
+      </c>
+      <c r="AI23">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="AJ23">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AL23">
+        <f t="shared" si="8"/>
+        <v>0.78</v>
+      </c>
+      <c r="AM23">
+        <v>0.68</v>
+      </c>
+      <c r="AN23">
+        <v>0.88</v>
+      </c>
+      <c r="AO23">
+        <f>AF23-AI23</f>
+        <v>22.85</v>
+      </c>
+      <c r="AP23" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ23" s="5">
+        <f>SQRT(AG23*AG23+AJ23*AJ23)</f>
+        <v>0.49497474683058323</v>
+      </c>
+      <c r="AR23" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS23">
+        <f>AO23*0.07</f>
+        <v>1.5995000000000001</v>
+      </c>
+      <c r="AU23">
+        <v>288</v>
+      </c>
+      <c r="AV23" s="6">
+        <f>AO23/AU23</f>
+        <v>7.9340277777777787E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:48">
+      <c r="D24">
         <f t="shared" si="6"/>
-        <v>2.0993000000000004</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D24">
-        <f t="shared" si="5"/>
         <v>0.98</v>
       </c>
       <c r="E24">
@@ -1396,17 +2475,67 @@
         <v>29.200000000000003</v>
       </c>
       <c r="H24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.85586213843118442</v>
       </c>
       <c r="I24">
+        <f t="shared" si="7"/>
+        <v>2.0440000000000005</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF24">
+        <v>25.1</v>
+      </c>
+      <c r="AG24">
+        <v>0.49</v>
+      </c>
+      <c r="AI24">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="AJ24">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AL24">
+        <f t="shared" si="8"/>
+        <v>0.98</v>
+      </c>
+      <c r="AM24">
+        <v>0.88</v>
+      </c>
+      <c r="AN24">
+        <v>1.08</v>
+      </c>
+      <c r="AO24">
+        <f>AF24-AI24</f>
+        <v>23.990000000000002</v>
+      </c>
+      <c r="AP24" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ24" s="5">
+        <f>SQRT(AG24*AG24+AJ24*AJ24)</f>
+        <v>0.49497474683058323</v>
+      </c>
+      <c r="AR24" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS24">
+        <f>AO24*0.07</f>
+        <v>1.6793000000000002</v>
+      </c>
+      <c r="AU24">
+        <v>288</v>
+      </c>
+      <c r="AV24" s="6">
+        <f>AO24/AU24</f>
+        <v>8.3298611111111115E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:48">
+      <c r="D25">
         <f t="shared" si="6"/>
-        <v>2.0440000000000005</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D25">
-        <f t="shared" si="5"/>
         <v>1.1800000000000002</v>
       </c>
       <c r="E25">
@@ -1419,17 +2548,67 @@
         <v>31.75</v>
       </c>
       <c r="H25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.0547511554864493</v>
       </c>
       <c r="I25">
+        <f t="shared" si="7"/>
+        <v>2.2225000000000001</v>
+      </c>
+      <c r="AE25" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF25">
+        <v>26.88</v>
+      </c>
+      <c r="AG25">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="AI25">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="AJ25">
+        <v>0.09</v>
+      </c>
+      <c r="AL25">
+        <f t="shared" si="8"/>
+        <v>1.1800000000000002</v>
+      </c>
+      <c r="AM25">
+        <v>1.08</v>
+      </c>
+      <c r="AN25">
+        <v>1.28</v>
+      </c>
+      <c r="AO25">
+        <f>AF25-AI25</f>
+        <v>26.31</v>
+      </c>
+      <c r="AP25" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ25" s="5">
+        <f>SQRT(AG25*AG25+AJ25*AJ25)</f>
+        <v>0.57706152185014026</v>
+      </c>
+      <c r="AR25" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS25">
+        <f>AO25*0.07</f>
+        <v>1.8417000000000001</v>
+      </c>
+      <c r="AU25">
+        <v>288</v>
+      </c>
+      <c r="AV25" s="6">
+        <f>AO25/AU25</f>
+        <v>9.1354166666666667E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:48">
+      <c r="D26">
         <f t="shared" si="6"/>
-        <v>2.2225000000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D26">
-        <f t="shared" si="5"/>
         <v>1.38</v>
       </c>
       <c r="E26">
@@ -1442,17 +2621,67 @@
         <v>38.24</v>
       </c>
       <c r="H26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.4314574163174458</v>
       </c>
       <c r="I26">
+        <f t="shared" si="7"/>
+        <v>2.6768000000000005</v>
+      </c>
+      <c r="AE26" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF26">
+        <v>28.82</v>
+      </c>
+      <c r="AG26">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="AI26">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="AJ26">
+        <v>0.09</v>
+      </c>
+      <c r="AL26">
+        <f t="shared" si="8"/>
+        <v>1.38</v>
+      </c>
+      <c r="AM26">
+        <v>1.28</v>
+      </c>
+      <c r="AN26">
+        <v>1.48</v>
+      </c>
+      <c r="AO26">
+        <f>AF26-AI26</f>
+        <v>28.25</v>
+      </c>
+      <c r="AP26" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ26" s="5">
+        <f>SQRT(AG26*AG26+AJ26*AJ26)</f>
+        <v>0.58694122363316747</v>
+      </c>
+      <c r="AR26" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS26">
+        <f>AO26*0.07</f>
+        <v>1.9775000000000003</v>
+      </c>
+      <c r="AU26">
+        <v>288</v>
+      </c>
+      <c r="AV26" s="6">
+        <f>AO26/AU26</f>
+        <v>9.8090277777777776E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:48">
+      <c r="D27">
         <f t="shared" si="6"/>
-        <v>2.6768000000000005</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D27">
-        <f t="shared" si="5"/>
         <v>1.58</v>
       </c>
       <c r="E27">
@@ -1465,12 +2694,1919 @@
         <v>39.35</v>
       </c>
       <c r="H27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="I27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.7545000000000002</v>
+      </c>
+      <c r="AE27" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF27">
+        <v>30.3</v>
+      </c>
+      <c r="AG27">
+        <v>1.55</v>
+      </c>
+      <c r="AI27">
+        <v>0</v>
+      </c>
+      <c r="AL27">
+        <f t="shared" si="8"/>
+        <v>1.58</v>
+      </c>
+      <c r="AM27">
+        <v>1.48</v>
+      </c>
+      <c r="AN27">
+        <v>1.68</v>
+      </c>
+      <c r="AO27">
+        <f>AF27-AI27</f>
+        <v>30.3</v>
+      </c>
+      <c r="AP27" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ27" s="5">
+        <f>SQRT(AG27*AG27+AJ27*AJ27)</f>
+        <v>1.55</v>
+      </c>
+      <c r="AR27" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS27">
+        <f>AO27*0.07</f>
+        <v>2.1210000000000004</v>
+      </c>
+      <c r="AU27">
+        <v>288</v>
+      </c>
+      <c r="AV27" s="6">
+        <f>AO27/AU27</f>
+        <v>0.10520833333333333</v>
+      </c>
+    </row>
+    <row r="28" spans="1:48">
+      <c r="AO28">
+        <f>AF28-AI28</f>
+        <v>0</v>
+      </c>
+      <c r="AP28" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ28" s="5">
+        <f>SQRT(AG28*AG28+AJ28*AJ28)</f>
+        <v>0</v>
+      </c>
+      <c r="AR28" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS28">
+        <f>AO28*0.07</f>
+        <v>0</v>
+      </c>
+      <c r="AV28" s="6" t="e">
+        <f>AO28/AU28</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="29" spans="1:48">
+      <c r="AF29" t="s">
+        <v>18</v>
+      </c>
+      <c r="AI29" t="s">
+        <v>18</v>
+      </c>
+      <c r="AO29" t="s">
+        <v>18</v>
+      </c>
+      <c r="AQ29" s="5">
+        <f>SQRT(AG29*AG29+AJ29*AJ29)</f>
+        <v>0</v>
+      </c>
+      <c r="AR29" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS29" t="s">
+        <v>18</v>
+      </c>
+      <c r="AV29" s="6" t="e">
+        <f>AO29/AU29</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="30" spans="1:48">
+      <c r="AE30" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF30">
+        <v>14.36</v>
+      </c>
+      <c r="AG30">
+        <v>0.43</v>
+      </c>
+      <c r="AI30">
+        <v>0.92</v>
+      </c>
+      <c r="AJ30">
+        <v>0.06</v>
+      </c>
+      <c r="AL30">
+        <f>(AM30+AN30)/2</f>
+        <v>-0.42000000000000004</v>
+      </c>
+      <c r="AM30">
+        <v>-0.52</v>
+      </c>
+      <c r="AN30">
+        <v>-0.32</v>
+      </c>
+      <c r="AO30">
+        <f>AF30-AI30</f>
+        <v>13.44</v>
+      </c>
+      <c r="AP30" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ30" s="5">
+        <f>SQRT(AG30*AG30+AJ30*AJ30)</f>
+        <v>0.43416586692184816</v>
+      </c>
+      <c r="AR30" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS30">
+        <f>AO30*0.07</f>
+        <v>0.94080000000000008</v>
+      </c>
+      <c r="AU30">
+        <v>211</v>
+      </c>
+      <c r="AV30" s="6">
+        <f>AO30/AU30</f>
+        <v>6.3696682464454979E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:48">
+      <c r="AE31" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF31">
+        <v>15.14</v>
+      </c>
+      <c r="AG31">
+        <v>0.38</v>
+      </c>
+      <c r="AI31">
+        <v>0.92</v>
+      </c>
+      <c r="AJ31">
+        <v>0.06</v>
+      </c>
+      <c r="AL31">
+        <f t="shared" ref="AL31:AL40" si="9">(AM31+AN31)/2</f>
+        <v>-0.22</v>
+      </c>
+      <c r="AM31">
+        <v>-0.32</v>
+      </c>
+      <c r="AN31">
+        <v>-0.12</v>
+      </c>
+      <c r="AO31">
+        <f>AF31-AI31</f>
+        <v>14.22</v>
+      </c>
+      <c r="AP31" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ31" s="5">
+        <f>SQRT(AG31*AG31+AJ31*AJ31)</f>
+        <v>0.38470768123342691</v>
+      </c>
+      <c r="AR31" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS31">
+        <f>AO31*0.07</f>
+        <v>0.99540000000000017</v>
+      </c>
+      <c r="AU31">
+        <v>211</v>
+      </c>
+      <c r="AV31" s="6">
+        <f>AO31/AU31</f>
+        <v>6.739336492890996E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:48">
+      <c r="AE32" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF32">
+        <v>14.79</v>
+      </c>
+      <c r="AG32">
+        <v>0.33</v>
+      </c>
+      <c r="AI32">
+        <v>1.06</v>
+      </c>
+      <c r="AJ32">
+        <v>0.05</v>
+      </c>
+      <c r="AL32">
+        <f t="shared" si="9"/>
+        <v>-1.9999999999999997E-2</v>
+      </c>
+      <c r="AM32">
+        <v>-0.12</v>
+      </c>
+      <c r="AN32">
+        <v>0.08</v>
+      </c>
+      <c r="AO32">
+        <f>AF32-AI32</f>
+        <v>13.729999999999999</v>
+      </c>
+      <c r="AP32" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ32" s="5">
+        <f>SQRT(AG32*AG32+AJ32*AJ32)</f>
+        <v>0.33376638536557274</v>
+      </c>
+      <c r="AR32" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS32">
+        <f>AO32*0.07</f>
+        <v>0.96109999999999995</v>
+      </c>
+      <c r="AU32">
+        <v>211</v>
+      </c>
+      <c r="AV32" s="6">
+        <f>AO32/AU32</f>
+        <v>6.5071090047393365E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="31:48">
+      <c r="AE33" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF33">
+        <v>14.96</v>
+      </c>
+      <c r="AG33">
+        <v>0.31</v>
+      </c>
+      <c r="AI33">
+        <v>1.06</v>
+      </c>
+      <c r="AJ33">
+        <v>0.05</v>
+      </c>
+      <c r="AL33">
+        <f t="shared" si="9"/>
+        <v>0.18000000000000002</v>
+      </c>
+      <c r="AM33">
+        <v>0.08</v>
+      </c>
+      <c r="AN33">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AO33">
+        <f>AF33-AI33</f>
+        <v>13.9</v>
+      </c>
+      <c r="AP33" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ33" s="5">
+        <f>SQRT(AG33*AG33+AJ33*AJ33)</f>
+        <v>0.31400636936215165</v>
+      </c>
+      <c r="AR33" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS33">
+        <f>AO33*0.07</f>
+        <v>0.97300000000000009</v>
+      </c>
+      <c r="AU33">
+        <v>211</v>
+      </c>
+      <c r="AV33" s="6">
+        <f>AO33/AU33</f>
+        <v>6.5876777251184834E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="31:48">
+      <c r="AE34" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF34">
+        <v>15.35</v>
+      </c>
+      <c r="AG34">
+        <v>0.3</v>
+      </c>
+      <c r="AI34">
+        <v>0.96</v>
+      </c>
+      <c r="AJ34">
+        <v>0.05</v>
+      </c>
+      <c r="AL34">
+        <f t="shared" si="9"/>
+        <v>0.38</v>
+      </c>
+      <c r="AM34">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AN34">
+        <v>0.48</v>
+      </c>
+      <c r="AO34">
+        <f>AF34-AI34</f>
+        <v>14.39</v>
+      </c>
+      <c r="AP34" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ34" s="5">
+        <f>SQRT(AG34*AG34+AJ34*AJ34)</f>
+        <v>0.30413812651491096</v>
+      </c>
+      <c r="AR34" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS34">
+        <f>AO34*0.07</f>
+        <v>1.0073000000000001</v>
+      </c>
+      <c r="AU34">
+        <v>211</v>
+      </c>
+      <c r="AV34" s="6">
+        <f>AO34/AU34</f>
+        <v>6.8199052132701429E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="31:48">
+      <c r="AE35" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF35">
+        <v>16.27</v>
+      </c>
+      <c r="AG35">
+        <v>0.3</v>
+      </c>
+      <c r="AI35">
+        <v>0.96</v>
+      </c>
+      <c r="AJ35">
+        <v>0.05</v>
+      </c>
+      <c r="AL35">
+        <f t="shared" si="9"/>
+        <v>0.58000000000000007</v>
+      </c>
+      <c r="AM35">
+        <v>0.48</v>
+      </c>
+      <c r="AN35">
+        <v>0.68</v>
+      </c>
+      <c r="AO35">
+        <f>AF35-AI35</f>
+        <v>15.309999999999999</v>
+      </c>
+      <c r="AP35" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ35" s="5">
+        <f>SQRT(AG35*AG35+AJ35*AJ35)</f>
+        <v>0.30413812651491096</v>
+      </c>
+      <c r="AR35" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS35">
+        <f>AO35*0.07</f>
+        <v>1.0717000000000001</v>
+      </c>
+      <c r="AU35">
+        <v>211</v>
+      </c>
+      <c r="AV35" s="6">
+        <f>AO35/AU35</f>
+        <v>7.2559241706161126E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="31:48">
+      <c r="AE36" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF36">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="AG36">
+        <v>0.31</v>
+      </c>
+      <c r="AI36">
+        <v>0.8</v>
+      </c>
+      <c r="AJ36">
+        <v>0.05</v>
+      </c>
+      <c r="AL36">
+        <f t="shared" si="9"/>
+        <v>0.78</v>
+      </c>
+      <c r="AM36">
+        <v>0.68</v>
+      </c>
+      <c r="AN36">
+        <v>0.88</v>
+      </c>
+      <c r="AO36">
+        <f>AF36-AI36</f>
+        <v>16.599999999999998</v>
+      </c>
+      <c r="AP36" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ36" s="5">
+        <f>SQRT(AG36*AG36+AJ36*AJ36)</f>
+        <v>0.31400636936215165</v>
+      </c>
+      <c r="AR36" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS36">
+        <f>AO36*0.07</f>
+        <v>1.1619999999999999</v>
+      </c>
+      <c r="AU36">
+        <v>211</v>
+      </c>
+      <c r="AV36" s="6">
+        <f>AO36/AU36</f>
+        <v>7.8672985781990515E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="31:48">
+      <c r="AE37" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF37">
+        <v>17.87</v>
+      </c>
+      <c r="AG37">
+        <v>0.32</v>
+      </c>
+      <c r="AI37">
+        <v>0.8</v>
+      </c>
+      <c r="AJ37">
+        <v>0.05</v>
+      </c>
+      <c r="AL37">
+        <f t="shared" si="9"/>
+        <v>0.98</v>
+      </c>
+      <c r="AM37">
+        <v>0.88</v>
+      </c>
+      <c r="AN37">
+        <v>1.08</v>
+      </c>
+      <c r="AO37">
+        <f>AF37-AI37</f>
+        <v>17.07</v>
+      </c>
+      <c r="AP37" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ37" s="5">
+        <f>SQRT(AG37*AG37+AJ37*AJ37)</f>
+        <v>0.32388269481403298</v>
+      </c>
+      <c r="AR37" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS37">
+        <f>AO37*0.07</f>
+        <v>1.1949000000000001</v>
+      </c>
+      <c r="AU37">
+        <v>211</v>
+      </c>
+      <c r="AV37" s="6">
+        <f>AO37/AU37</f>
+        <v>8.0900473933649297E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="31:48">
+      <c r="AE38" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF38">
+        <v>19.22</v>
+      </c>
+      <c r="AG38">
+        <v>0.39</v>
+      </c>
+      <c r="AI38">
+        <v>0.37</v>
+      </c>
+      <c r="AJ38">
+        <v>0.05</v>
+      </c>
+      <c r="AL38">
+        <f t="shared" si="9"/>
+        <v>1.1800000000000002</v>
+      </c>
+      <c r="AM38">
+        <v>1.08</v>
+      </c>
+      <c r="AN38">
+        <v>1.28</v>
+      </c>
+      <c r="AO38">
+        <f>AF38-AI38</f>
+        <v>18.849999999999998</v>
+      </c>
+      <c r="AP38" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ38" s="5">
+        <f>SQRT(AG38*AG38+AJ38*AJ38)</f>
+        <v>0.39319206502675003</v>
+      </c>
+      <c r="AR38" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS38">
+        <f>AO38*0.07</f>
+        <v>1.3194999999999999</v>
+      </c>
+      <c r="AU38">
+        <v>211</v>
+      </c>
+      <c r="AV38" s="6">
+        <f>AO38/AU38</f>
+        <v>8.9336492890995253E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="31:48">
+      <c r="AE39" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF39">
+        <v>21.46</v>
+      </c>
+      <c r="AG39">
+        <v>0.43</v>
+      </c>
+      <c r="AI39">
+        <v>0.37</v>
+      </c>
+      <c r="AJ39">
+        <v>0.05</v>
+      </c>
+      <c r="AL39">
+        <f t="shared" si="9"/>
+        <v>1.38</v>
+      </c>
+      <c r="AM39">
+        <v>1.28</v>
+      </c>
+      <c r="AN39">
+        <v>1.48</v>
+      </c>
+      <c r="AO39">
+        <f>AF39-AI39</f>
+        <v>21.09</v>
+      </c>
+      <c r="AP39" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ39" s="5">
+        <f>SQRT(AG39*AG39+AJ39*AJ39)</f>
+        <v>0.43289721643826723</v>
+      </c>
+      <c r="AR39" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS39">
+        <f>AO39*0.07</f>
+        <v>1.4763000000000002</v>
+      </c>
+      <c r="AU39">
+        <v>211</v>
+      </c>
+      <c r="AV39" s="6">
+        <f>AO39/AU39</f>
+        <v>9.9952606635071092E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="31:48">
+      <c r="AE40" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF40">
+        <v>20.13</v>
+      </c>
+      <c r="AG40">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AI40">
+        <v>0</v>
+      </c>
+      <c r="AL40">
+        <f t="shared" si="9"/>
+        <v>1.58</v>
+      </c>
+      <c r="AM40">
+        <v>1.48</v>
+      </c>
+      <c r="AN40">
+        <v>1.68</v>
+      </c>
+      <c r="AO40">
+        <f>AF40-AI40</f>
+        <v>20.13</v>
+      </c>
+      <c r="AP40" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ40" s="5">
+        <f>SQRT(AG40*AG40+AJ40*AJ40)</f>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AR40" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS40">
+        <f>AO40*0.07</f>
+        <v>1.4091</v>
+      </c>
+      <c r="AU40">
+        <v>211</v>
+      </c>
+      <c r="AV40" s="6">
+        <f>AO40/AU40</f>
+        <v>9.5402843601895729E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="31:48">
+      <c r="AO41">
+        <f>AF41-AI41</f>
+        <v>0</v>
+      </c>
+      <c r="AP41" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ41" s="5">
+        <f>SQRT(AG41*AG41+AJ41*AJ41)</f>
+        <v>0</v>
+      </c>
+      <c r="AR41" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS41">
+        <f>AO41*0.07</f>
+        <v>0</v>
+      </c>
+      <c r="AV41" s="6" t="e">
+        <f>AO41/AU41</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="42" spans="31:48">
+      <c r="AF42" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI42" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO42" t="s">
+        <v>19</v>
+      </c>
+      <c r="AP42" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ42" s="5">
+        <f>SQRT(AG42*AG42+AJ42*AJ42)</f>
+        <v>0</v>
+      </c>
+      <c r="AR42" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS42" t="s">
+        <v>19</v>
+      </c>
+      <c r="AV42" s="6" t="e">
+        <f>AO42/AU42</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="43" spans="31:48">
+      <c r="AE43" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF43">
+        <v>9.2799999999999994</v>
+      </c>
+      <c r="AG43">
+        <v>0.3</v>
+      </c>
+      <c r="AI43">
+        <v>0.78</v>
+      </c>
+      <c r="AJ43">
+        <v>0.05</v>
+      </c>
+      <c r="AL43">
+        <f>(AM43+AN43)/2</f>
+        <v>-0.42000000000000004</v>
+      </c>
+      <c r="AM43">
+        <v>-0.52</v>
+      </c>
+      <c r="AN43">
+        <v>-0.32</v>
+      </c>
+      <c r="AO43">
+        <f>AF43-AI43</f>
+        <v>8.5</v>
+      </c>
+      <c r="AP43" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ43" s="5">
+        <f>SQRT(AG43*AG43+AJ43*AJ43)</f>
+        <v>0.30413812651491096</v>
+      </c>
+      <c r="AR43" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS43">
+        <f>AO43*0.07</f>
+        <v>0.59500000000000008</v>
+      </c>
+      <c r="AU43">
+        <v>146</v>
+      </c>
+      <c r="AV43" s="6">
+        <f>AO43/AU43</f>
+        <v>5.8219178082191778E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="31:48">
+      <c r="AE44" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF44">
+        <v>9.4600000000000009</v>
+      </c>
+      <c r="AG44">
+        <v>0.25</v>
+      </c>
+      <c r="AI44">
+        <v>0.78</v>
+      </c>
+      <c r="AJ44">
+        <v>0.05</v>
+      </c>
+      <c r="AL44">
+        <f t="shared" ref="AL44:AL53" si="10">(AM44+AN44)/2</f>
+        <v>-0.22</v>
+      </c>
+      <c r="AM44">
+        <v>-0.32</v>
+      </c>
+      <c r="AN44">
+        <v>-0.12</v>
+      </c>
+      <c r="AO44">
+        <f>AF44-AI44</f>
+        <v>8.6800000000000015</v>
+      </c>
+      <c r="AP44" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ44" s="5">
+        <f>SQRT(AG44*AG44+AJ44*AJ44)</f>
+        <v>0.25495097567963926</v>
+      </c>
+      <c r="AR44" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS44">
+        <f>AO44*0.07</f>
+        <v>0.60760000000000014</v>
+      </c>
+      <c r="AU44">
+        <v>146</v>
+      </c>
+      <c r="AV44" s="6">
+        <f>AO44/AU44</f>
+        <v>5.9452054794520558E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="31:48">
+      <c r="AE45" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF45">
+        <v>9.4600000000000009</v>
+      </c>
+      <c r="AG45">
+        <v>0.23</v>
+      </c>
+      <c r="AI45">
+        <v>0.8</v>
+      </c>
+      <c r="AJ45">
+        <v>0.04</v>
+      </c>
+      <c r="AL45">
+        <f t="shared" si="10"/>
+        <v>-1.9999999999999997E-2</v>
+      </c>
+      <c r="AM45">
+        <v>-0.12</v>
+      </c>
+      <c r="AN45">
+        <v>0.08</v>
+      </c>
+      <c r="AO45">
+        <f>AF45-AI45</f>
+        <v>8.66</v>
+      </c>
+      <c r="AP45" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ45" s="5">
+        <f>SQRT(AG45*AG45+AJ45*AJ45)</f>
+        <v>0.23345235059857505</v>
+      </c>
+      <c r="AR45" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS45">
+        <f>AO45*0.07</f>
+        <v>0.60620000000000007</v>
+      </c>
+      <c r="AU45">
+        <v>146</v>
+      </c>
+      <c r="AV45" s="6">
+        <f>AO45/AU45</f>
+        <v>5.9315068493150686E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="31:48">
+      <c r="AE46" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF46">
+        <v>9.34</v>
+      </c>
+      <c r="AG46">
+        <v>0.21</v>
+      </c>
+      <c r="AI46">
+        <v>0.8</v>
+      </c>
+      <c r="AJ46">
+        <v>0.04</v>
+      </c>
+      <c r="AL46">
+        <f t="shared" si="10"/>
+        <v>0.18000000000000002</v>
+      </c>
+      <c r="AM46">
+        <v>0.08</v>
+      </c>
+      <c r="AN46">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AO46">
+        <f>AF46-AI46</f>
+        <v>8.5399999999999991</v>
+      </c>
+      <c r="AP46" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ46" s="5">
+        <f>SQRT(AG46*AG46+AJ46*AJ46)</f>
+        <v>0.21377558326431947</v>
+      </c>
+      <c r="AR46" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS46">
+        <f>AO46*0.07</f>
+        <v>0.5978</v>
+      </c>
+      <c r="AU46">
+        <v>146</v>
+      </c>
+      <c r="AV46" s="6">
+        <f>AO46/AU46</f>
+        <v>5.8493150684931501E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="31:48">
+      <c r="AE47" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF47">
+        <v>9.64</v>
+      </c>
+      <c r="AG47">
+        <v>0.21</v>
+      </c>
+      <c r="AI47">
+        <v>0.7</v>
+      </c>
+      <c r="AJ47">
+        <v>0.04</v>
+      </c>
+      <c r="AL47">
+        <f t="shared" si="10"/>
+        <v>0.38</v>
+      </c>
+      <c r="AM47">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AN47">
+        <v>0.48</v>
+      </c>
+      <c r="AO47">
+        <f>AF47-AI47</f>
+        <v>8.9400000000000013</v>
+      </c>
+      <c r="AP47" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ47" s="5">
+        <f>SQRT(AG47*AG47+AJ47*AJ47)</f>
+        <v>0.21377558326431947</v>
+      </c>
+      <c r="AR47" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS47">
+        <f>AO47*0.07</f>
+        <v>0.62580000000000013</v>
+      </c>
+      <c r="AU47">
+        <v>146</v>
+      </c>
+      <c r="AV47" s="6">
+        <f>AO47/AU47</f>
+        <v>6.1232876712328778E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="31:48">
+      <c r="AE48" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF48">
+        <v>9.92</v>
+      </c>
+      <c r="AG48">
+        <v>0.23</v>
+      </c>
+      <c r="AI48">
+        <v>0.7</v>
+      </c>
+      <c r="AJ48">
+        <v>0.04</v>
+      </c>
+      <c r="AL48">
+        <f t="shared" si="10"/>
+        <v>0.58000000000000007</v>
+      </c>
+      <c r="AM48">
+        <v>0.48</v>
+      </c>
+      <c r="AN48">
+        <v>0.68</v>
+      </c>
+      <c r="AO48">
+        <f>AF48-AI48</f>
+        <v>9.2200000000000006</v>
+      </c>
+      <c r="AP48" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ48" s="5">
+        <f>SQRT(AG48*AG48+AJ48*AJ48)</f>
+        <v>0.23345235059857505</v>
+      </c>
+      <c r="AR48" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS48">
+        <f>AO48*0.07</f>
+        <v>0.64540000000000008</v>
+      </c>
+      <c r="AU48">
+        <v>146</v>
+      </c>
+      <c r="AV48" s="6">
+        <f>AO48/AU48</f>
+        <v>6.3150684931506856E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="31:48">
+      <c r="AE49" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF49">
+        <v>10.97</v>
+      </c>
+      <c r="AG49">
+        <v>0.23</v>
+      </c>
+      <c r="AI49">
+        <v>0.54</v>
+      </c>
+      <c r="AJ49">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="AL49">
+        <f t="shared" si="10"/>
+        <v>0.78</v>
+      </c>
+      <c r="AM49">
+        <v>0.68</v>
+      </c>
+      <c r="AN49">
+        <v>0.88</v>
+      </c>
+      <c r="AO49">
+        <f>AF49-AI49</f>
+        <v>10.43</v>
+      </c>
+      <c r="AP49" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ49" s="5">
+        <f>SQRT(AG49*AG49+AJ49*AJ49)</f>
+        <v>0.23311799587333451</v>
+      </c>
+      <c r="AR49" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS49">
+        <f>AO49*0.07</f>
+        <v>0.73010000000000008</v>
+      </c>
+      <c r="AU49">
+        <v>146</v>
+      </c>
+      <c r="AV49" s="6">
+        <f>AO49/AU49</f>
+        <v>7.1438356164383557E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="31:48">
+      <c r="AE50" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF50">
+        <v>11.53</v>
+      </c>
+      <c r="AG50">
+        <v>0.24</v>
+      </c>
+      <c r="AI50">
+        <v>0.54</v>
+      </c>
+      <c r="AJ50">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="AL50">
+        <f t="shared" si="10"/>
+        <v>0.98</v>
+      </c>
+      <c r="AM50">
+        <v>0.88</v>
+      </c>
+      <c r="AN50">
+        <v>1.08</v>
+      </c>
+      <c r="AO50">
+        <f>AF50-AI50</f>
+        <v>10.989999999999998</v>
+      </c>
+      <c r="AP50" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ50" s="5">
+        <f>SQRT(AG50*AG50+AJ50*AJ50)</f>
+        <v>0.24298971171636052</v>
+      </c>
+      <c r="AR50" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS50">
+        <f>AO50*0.07</f>
+        <v>0.76929999999999998</v>
+      </c>
+      <c r="AU50">
+        <v>146</v>
+      </c>
+      <c r="AV50" s="6">
+        <f>AO50/AU50</f>
+        <v>7.5273972602739714E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="31:48">
+      <c r="AE51" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF51">
+        <v>12.25</v>
+      </c>
+      <c r="AG51">
+        <v>0.26</v>
+      </c>
+      <c r="AI51">
+        <v>0.21</v>
+      </c>
+      <c r="AJ51">
+        <v>0.03</v>
+      </c>
+      <c r="AL51">
+        <f t="shared" si="10"/>
+        <v>1.1800000000000002</v>
+      </c>
+      <c r="AM51">
+        <v>1.08</v>
+      </c>
+      <c r="AN51">
+        <v>1.28</v>
+      </c>
+      <c r="AO51">
+        <f>AF51-AI51</f>
+        <v>12.04</v>
+      </c>
+      <c r="AP51" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ51" s="5">
+        <f>SQRT(AG51*AG51+AJ51*AJ51)</f>
+        <v>0.261725046566048</v>
+      </c>
+      <c r="AR51" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS51">
+        <f>AO51*0.07</f>
+        <v>0.84279999999999999</v>
+      </c>
+      <c r="AU51">
+        <v>146</v>
+      </c>
+      <c r="AV51" s="6">
+        <f>AO51/AU51</f>
+        <v>8.2465753424657534E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="31:48">
+      <c r="AE52" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF52">
+        <v>13.63</v>
+      </c>
+      <c r="AG52">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AI52">
+        <v>0.21</v>
+      </c>
+      <c r="AJ52">
+        <v>0.03</v>
+      </c>
+      <c r="AL52">
+        <f t="shared" si="10"/>
+        <v>1.38</v>
+      </c>
+      <c r="AM52">
+        <v>1.28</v>
+      </c>
+      <c r="AN52">
+        <v>1.48</v>
+      </c>
+      <c r="AO52">
+        <f>AF52-AI52</f>
+        <v>13.42</v>
+      </c>
+      <c r="AP52" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ52" s="5">
+        <f>SQRT(AG52*AG52+AJ52*AJ52)</f>
+        <v>0.28160255680657448</v>
+      </c>
+      <c r="AR52" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS52">
+        <f>AO52*0.07</f>
+        <v>0.93940000000000012</v>
+      </c>
+      <c r="AU52">
+        <v>146</v>
+      </c>
+      <c r="AV52" s="6">
+        <f>AO52/AU52</f>
+        <v>9.1917808219178082E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="31:48">
+      <c r="AE53" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF53">
+        <v>16.38</v>
+      </c>
+      <c r="AG53">
+        <v>0.98</v>
+      </c>
+      <c r="AI53">
+        <v>0</v>
+      </c>
+      <c r="AL53">
+        <f t="shared" si="10"/>
+        <v>1.58</v>
+      </c>
+      <c r="AM53">
+        <v>1.48</v>
+      </c>
+      <c r="AN53">
+        <v>1.68</v>
+      </c>
+      <c r="AO53">
+        <f>AF53-AI53</f>
+        <v>16.38</v>
+      </c>
+      <c r="AP53" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ53" s="5">
+        <f>SQRT(AG53*AG53+AJ53*AJ53)</f>
+        <v>0.98</v>
+      </c>
+      <c r="AR53" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS53">
+        <f>AO53*0.07</f>
+        <v>1.1466000000000001</v>
+      </c>
+      <c r="AU53">
+        <v>146</v>
+      </c>
+      <c r="AV53" s="6">
+        <f>AO53/AU53</f>
+        <v>0.1121917808219178</v>
+      </c>
+    </row>
+    <row r="54" spans="31:48">
+      <c r="AO54">
+        <f>AF54-AI54</f>
+        <v>0</v>
+      </c>
+      <c r="AP54" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ54" s="5">
+        <f>SQRT(AG54*AG54+AJ54*AJ54)</f>
+        <v>0</v>
+      </c>
+      <c r="AR54" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS54">
+        <f>AO54*0.07</f>
+        <v>0</v>
+      </c>
+      <c r="AV54" s="6" t="e">
+        <f>AO54/AU54</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="55" spans="31:48">
+      <c r="AF55" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI55" t="s">
+        <v>20</v>
+      </c>
+      <c r="AO55" t="s">
+        <v>20</v>
+      </c>
+      <c r="AP55" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ55" s="5">
+        <f>SQRT(AG55*AG55+AJ55*AJ55)</f>
+        <v>0</v>
+      </c>
+      <c r="AR55" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS55" t="s">
+        <v>20</v>
+      </c>
+      <c r="AV55" s="6" t="e">
+        <f>AO55/AU55</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="56" spans="31:48">
+      <c r="AE56" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF56">
+        <v>5.84</v>
+      </c>
+      <c r="AG56">
+        <v>0.21</v>
+      </c>
+      <c r="AI56">
+        <v>0.51</v>
+      </c>
+      <c r="AJ56">
+        <v>0.04</v>
+      </c>
+      <c r="AL56">
+        <f>(AM56+AN56)/2</f>
+        <v>-0.42000000000000004</v>
+      </c>
+      <c r="AM56">
+        <v>-0.52</v>
+      </c>
+      <c r="AN56">
+        <v>-0.32</v>
+      </c>
+      <c r="AO56">
+        <f>AF56-AI56</f>
+        <v>5.33</v>
+      </c>
+      <c r="AP56" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ56" s="5">
+        <f>SQRT(AG56*AG56+AJ56*AJ56)</f>
+        <v>0.21377558326431947</v>
+      </c>
+      <c r="AR56" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS56">
+        <f>AO56*0.07</f>
+        <v>0.37310000000000004</v>
+      </c>
+      <c r="AU56">
+        <v>85</v>
+      </c>
+      <c r="AV56" s="6">
+        <f>AO56/AU56</f>
+        <v>6.2705882352941181E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="31:48">
+      <c r="AE57" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF57">
+        <v>6.03</v>
+      </c>
+      <c r="AG57">
+        <v>0.18</v>
+      </c>
+      <c r="AI57">
+        <v>0.51</v>
+      </c>
+      <c r="AJ57">
+        <v>0.04</v>
+      </c>
+      <c r="AL57">
+        <f t="shared" ref="AL57:AL66" si="11">(AM57+AN57)/2</f>
+        <v>-0.22</v>
+      </c>
+      <c r="AM57">
+        <v>-0.32</v>
+      </c>
+      <c r="AN57">
+        <v>-0.12</v>
+      </c>
+      <c r="AO57">
+        <f>AF57-AI57</f>
+        <v>5.5200000000000005</v>
+      </c>
+      <c r="AP57" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ57" s="5">
+        <f>SQRT(AG57*AG57+AJ57*AJ57)</f>
+        <v>0.18439088914585774</v>
+      </c>
+      <c r="AR57" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS57">
+        <f>AO57*0.07</f>
+        <v>0.38640000000000008</v>
+      </c>
+      <c r="AU57">
+        <v>85</v>
+      </c>
+      <c r="AV57" s="6">
+        <f>AO57/AU57</f>
+        <v>6.4941176470588238E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="31:48">
+      <c r="AE58" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF58">
+        <v>6.07</v>
+      </c>
+      <c r="AG58">
+        <v>0.19</v>
+      </c>
+      <c r="AI58">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AJ58">
+        <v>0.03</v>
+      </c>
+      <c r="AL58">
+        <f t="shared" si="11"/>
+        <v>-1.9999999999999997E-2</v>
+      </c>
+      <c r="AM58">
+        <v>-0.12</v>
+      </c>
+      <c r="AN58">
+        <v>0.08</v>
+      </c>
+      <c r="AO58">
+        <f>AF58-AI58</f>
+        <v>5.5200000000000005</v>
+      </c>
+      <c r="AP58" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ58" s="5">
+        <f>SQRT(AG58*AG58+AJ58*AJ58)</f>
+        <v>0.19235384061671346</v>
+      </c>
+      <c r="AR58" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS58">
+        <f>AO58*0.07</f>
+        <v>0.38640000000000008</v>
+      </c>
+      <c r="AU58">
+        <v>85</v>
+      </c>
+      <c r="AV58" s="6">
+        <f>AO58/AU58</f>
+        <v>6.4941176470588238E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="31:48">
+      <c r="AE59" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF59">
+        <v>5.98</v>
+      </c>
+      <c r="AG59">
+        <v>0.16</v>
+      </c>
+      <c r="AI59">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AJ59">
+        <v>0.03</v>
+      </c>
+      <c r="AL59">
+        <f t="shared" si="11"/>
+        <v>0.18000000000000002</v>
+      </c>
+      <c r="AM59">
+        <v>0.08</v>
+      </c>
+      <c r="AN59">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AO59">
+        <f>AF59-AI59</f>
+        <v>5.4300000000000006</v>
+      </c>
+      <c r="AP59" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ59" s="5">
+        <f>SQRT(AG59*AG59+AJ59*AJ59)</f>
+        <v>0.16278820596099708</v>
+      </c>
+      <c r="AR59" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS59">
+        <f>AO59*0.07</f>
+        <v>0.3801000000000001</v>
+      </c>
+      <c r="AU59">
+        <v>85</v>
+      </c>
+      <c r="AV59" s="6">
+        <f>AO59/AU59</f>
+        <v>6.3882352941176473E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="31:48">
+      <c r="AE60" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF60">
+        <v>5.96</v>
+      </c>
+      <c r="AG60">
+        <v>0.15</v>
+      </c>
+      <c r="AI60">
+        <v>0.49</v>
+      </c>
+      <c r="AJ60">
+        <v>0.03</v>
+      </c>
+      <c r="AL60">
+        <f t="shared" si="11"/>
+        <v>0.38</v>
+      </c>
+      <c r="AM60">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AN60">
+        <v>0.48</v>
+      </c>
+      <c r="AO60">
+        <f>AF60-AI60</f>
+        <v>5.47</v>
+      </c>
+      <c r="AP60" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ60" s="5">
+        <f>SQRT(AG60*AG60+AJ60*AJ60)</f>
+        <v>0.15297058540778355</v>
+      </c>
+      <c r="AR60" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS60">
+        <f>AO60*0.07</f>
+        <v>0.38290000000000002</v>
+      </c>
+      <c r="AU60">
+        <v>85</v>
+      </c>
+      <c r="AV60" s="6">
+        <f>AO60/AU60</f>
+        <v>6.4352941176470585E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="31:48">
+      <c r="AE61" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF61">
+        <v>6.39</v>
+      </c>
+      <c r="AG61">
+        <v>0.16</v>
+      </c>
+      <c r="AI61">
+        <v>0.49</v>
+      </c>
+      <c r="AJ61">
+        <v>0.03</v>
+      </c>
+      <c r="AL61">
+        <f t="shared" si="11"/>
+        <v>0.58000000000000007</v>
+      </c>
+      <c r="AM61">
+        <v>0.48</v>
+      </c>
+      <c r="AN61">
+        <v>0.68</v>
+      </c>
+      <c r="AO61">
+        <f>AF61-AI61</f>
+        <v>5.8999999999999995</v>
+      </c>
+      <c r="AP61" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ61" s="5">
+        <f>SQRT(AG61*AG61+AJ61*AJ61)</f>
+        <v>0.16278820596099708</v>
+      </c>
+      <c r="AR61" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS61">
+        <f>AO61*0.07</f>
+        <v>0.41299999999999998</v>
+      </c>
+      <c r="AU61">
+        <v>85</v>
+      </c>
+      <c r="AV61" s="6">
+        <f>AO61/AU61</f>
+        <v>6.9411764705882353E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="31:48">
+      <c r="AE62" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF62">
+        <v>7.05</v>
+      </c>
+      <c r="AG62">
+        <v>0.17</v>
+      </c>
+      <c r="AI62">
+        <v>0.36</v>
+      </c>
+      <c r="AJ62">
+        <v>0.03</v>
+      </c>
+      <c r="AL62">
+        <f t="shared" si="11"/>
+        <v>0.78</v>
+      </c>
+      <c r="AM62">
+        <v>0.68</v>
+      </c>
+      <c r="AN62">
+        <v>0.88</v>
+      </c>
+      <c r="AO62">
+        <f>AF62-AI62</f>
+        <v>6.6899999999999995</v>
+      </c>
+      <c r="AP62" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ62" s="5">
+        <f>SQRT(AG62*AG62+AJ62*AJ62)</f>
+        <v>0.17262676501632071</v>
+      </c>
+      <c r="AR62" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS62">
+        <f>AO62*0.07</f>
+        <v>0.46829999999999999</v>
+      </c>
+      <c r="AU62">
+        <v>85</v>
+      </c>
+      <c r="AV62" s="6">
+        <f>AO62/AU62</f>
+        <v>7.8705882352941167E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="31:48">
+      <c r="AE63" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF63">
+        <v>7.55</v>
+      </c>
+      <c r="AG63">
+        <v>0.19</v>
+      </c>
+      <c r="AI63">
+        <v>0.36</v>
+      </c>
+      <c r="AJ63">
+        <v>0.03</v>
+      </c>
+      <c r="AL63">
+        <f t="shared" si="11"/>
+        <v>0.98</v>
+      </c>
+      <c r="AM63">
+        <v>0.88</v>
+      </c>
+      <c r="AN63">
+        <v>1.08</v>
+      </c>
+      <c r="AO63">
+        <f>AF63-AI63</f>
+        <v>7.1899999999999995</v>
+      </c>
+      <c r="AP63" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ63" s="5">
+        <f>SQRT(AG63*AG63+AJ63*AJ63)</f>
+        <v>0.19235384061671346</v>
+      </c>
+      <c r="AR63" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS63">
+        <f>AO63*0.07</f>
+        <v>0.50329999999999997</v>
+      </c>
+      <c r="AU63">
+        <v>85</v>
+      </c>
+      <c r="AV63" s="6">
+        <f>AO63/AU63</f>
+        <v>8.4588235294117645E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="31:48">
+      <c r="AE64" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF64">
+        <v>8.43</v>
+      </c>
+      <c r="AG64">
+        <v>0.2</v>
+      </c>
+      <c r="AI64">
+        <v>0.31</v>
+      </c>
+      <c r="AJ64">
+        <v>0.06</v>
+      </c>
+      <c r="AL64">
+        <f t="shared" si="11"/>
+        <v>1.1800000000000002</v>
+      </c>
+      <c r="AM64">
+        <v>1.08</v>
+      </c>
+      <c r="AN64">
+        <v>1.28</v>
+      </c>
+      <c r="AO64">
+        <f>AF64-AI64</f>
+        <v>8.1199999999999992</v>
+      </c>
+      <c r="AP64" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ64" s="5">
+        <f>SQRT(AG64*AG64+AJ64*AJ64)</f>
+        <v>0.20880613017821101</v>
+      </c>
+      <c r="AR64" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS64">
+        <f>AO64*0.07</f>
+        <v>0.56840000000000002</v>
+      </c>
+      <c r="AU64">
+        <v>85</v>
+      </c>
+      <c r="AV64" s="6">
+        <f>AO64/AU64</f>
+        <v>9.5529411764705877E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="31:48">
+      <c r="AE65" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF65">
+        <v>9.52</v>
+      </c>
+      <c r="AG65">
+        <v>0.22</v>
+      </c>
+      <c r="AI65">
+        <v>0.31</v>
+      </c>
+      <c r="AJ65">
+        <v>0.06</v>
+      </c>
+      <c r="AL65">
+        <f t="shared" si="11"/>
+        <v>1.38</v>
+      </c>
+      <c r="AM65">
+        <v>1.28</v>
+      </c>
+      <c r="AN65">
+        <v>1.48</v>
+      </c>
+      <c r="AO65">
+        <f>AF65-AI65</f>
+        <v>9.2099999999999991</v>
+      </c>
+      <c r="AP65" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ65" s="5">
+        <f>SQRT(AG65*AG65+AJ65*AJ65)</f>
+        <v>0.22803508501982758</v>
+      </c>
+      <c r="AR65" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS65">
+        <f>AO65*0.07</f>
+        <v>0.64470000000000005</v>
+      </c>
+      <c r="AU65">
+        <v>85</v>
+      </c>
+      <c r="AV65" s="6">
+        <f>AO65/AU65</f>
+        <v>0.10835294117647058</v>
+      </c>
+    </row>
+    <row r="66" spans="31:48">
+      <c r="AE66" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF66">
+        <v>10.73</v>
+      </c>
+      <c r="AG66">
+        <v>1.31</v>
+      </c>
+      <c r="AI66">
+        <v>0</v>
+      </c>
+      <c r="AL66">
+        <f t="shared" si="11"/>
+        <v>1.58</v>
+      </c>
+      <c r="AM66">
+        <v>1.48</v>
+      </c>
+      <c r="AN66">
+        <v>1.68</v>
+      </c>
+      <c r="AO66">
+        <f>AF66-AI66</f>
+        <v>10.73</v>
+      </c>
+      <c r="AP66" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ66" s="5">
+        <f>SQRT(AG66*AG66+AJ66*AJ66)</f>
+        <v>1.31</v>
+      </c>
+      <c r="AR66" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS66">
+        <f>AO66*0.07</f>
+        <v>0.7511000000000001</v>
+      </c>
+      <c r="AU66">
+        <v>85</v>
+      </c>
+      <c r="AV66" s="6">
+        <f>AO66/AU66</f>
+        <v>0.12623529411764706</v>
       </c>
     </row>
   </sheetData>
@@ -1479,15 +4615,25 @@
     <hyperlink ref="A1" r:id="rId1" xr:uid="{C0485903-CAD2-4AFC-BE24-82C0599D5733}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{442522CB-9026-483E-9FA1-CFE3429FB421}">
   <dimension ref="A1:X17"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" ht="15">
       <c r="A1">
         <v>-3.52</v>
       </c>
@@ -1542,7 +4688,7 @@
       <c r="W1" s="3"/>
       <c r="X1" s="3"/>
     </row>
-    <row r="2" spans="1:24" ht="15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:24" ht="15">
       <c r="A2">
         <v>-3.32</v>
       </c>
@@ -1607,7 +4753,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:24" ht="15">
       <c r="A3">
         <v>-3.12</v>
       </c>
@@ -1672,7 +4818,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:24" ht="15">
       <c r="A4">
         <v>-2.92</v>
       </c>
@@ -1737,7 +4883,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:24" ht="15">
       <c r="A5">
         <v>-2.72</v>
       </c>
@@ -1802,7 +4948,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:24" ht="15">
       <c r="A6">
         <v>-2.52</v>
       </c>
@@ -1867,7 +5013,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:24" ht="15">
       <c r="A7">
         <v>-2.3199999999999998</v>
       </c>
@@ -1932,7 +5078,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:24" ht="15">
       <c r="A8">
         <v>-2.12</v>
       </c>
@@ -1997,7 +5143,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:24" ht="15">
       <c r="A9">
         <v>-1.92</v>
       </c>
@@ -2062,7 +5208,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:24" ht="15">
       <c r="A10">
         <v>-1.72</v>
       </c>
@@ -2127,7 +5273,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:24" ht="15">
       <c r="A11">
         <v>-1.52</v>
       </c>
@@ -2192,7 +5338,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:24" ht="15">
       <c r="A12">
         <v>-1.32</v>
       </c>
@@ -2257,7 +5403,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:24" ht="15">
       <c r="A13">
         <v>-1.1200000000000001</v>
       </c>
@@ -2322,7 +5468,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:24" ht="15">
       <c r="A14">
         <v>-0.92</v>
       </c>
@@ -2387,7 +5533,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:24" ht="15">
       <c r="A15">
         <v>-0.72</v>
       </c>
@@ -2452,7 +5598,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:24" ht="15">
       <c r="A16">
         <v>-0.52</v>
       </c>
@@ -2517,7 +5663,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="17" spans="17:24" ht="15" x14ac:dyDescent="0.35">
+    <row r="17" spans="17:24" ht="15">
       <c r="Q17" s="1">
         <v>5.2</v>
       </c>
